--- a/test-artifact/web-tests.xlsx
+++ b/test-artifact/web-tests.xlsx
@@ -6,10 +6,20 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="All Tests" sheetId="2" r:id="rId2"/>
     <sheet name="Authentication" sheetId="3" r:id="rId3"/>
-    <sheet name="Bracket Management" sheetId="4" r:id="rId4"/>
-    <sheet name="Multi-Sport Tournaments" sheetId="5" r:id="rId5"/>
-    <sheet name="Tournament Management" sheetId="6" r:id="rId6"/>
-    <sheet name="Member Management" sheetId="7" r:id="rId7"/>
+    <sheet name="Home Landing Portal" sheetId="4" r:id="rId4"/>
+    <sheet name="Bracket Management" sheetId="5" r:id="rId5"/>
+    <sheet name="Badminton Matches" sheetId="6" r:id="rId6"/>
+    <sheet name="Carrom Matches" sheetId="7" r:id="rId7"/>
+    <sheet name="Chess Matches" sheetId="8" r:id="rId8"/>
+    <sheet name="Cricket Matches" sheetId="9" r:id="rId9"/>
+    <sheet name="Dual Division Matches" sheetId="10" r:id="rId10"/>
+    <sheet name="Match Arena &amp; Rounds" sheetId="11" r:id="rId11"/>
+    <sheet name="Table Tennis Matches" sheetId="12" r:id="rId12"/>
+    <sheet name="Multi-Sport Tournaments" sheetId="13" r:id="rId13"/>
+    <sheet name="Notification Center" sheetId="14" r:id="rId14"/>
+    <sheet name="Server Health &amp; Downtime" sheetId="15" r:id="rId15"/>
+    <sheet name="Tournament Management" sheetId="16" r:id="rId16"/>
+    <sheet name="Member Management" sheetId="17" r:id="rId17"/>
   </sheets>
 </workbook>
 </file>
@@ -403,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B29"/>
   <cols>
     <col min="1" max="1" width="35.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -422,7 +432,7 @@
         <v>Generated At</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-14</v>
       </c>
     </row>
     <row r="3">
@@ -470,7 +480,7 @@
         <v>Total Automated Scenarios</v>
       </c>
       <c r="B8">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -478,7 +488,7 @@
         <v>Passing Scenarios</v>
       </c>
       <c r="B9">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -515,62 +525,142 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bracket Management Module</v>
+        <v>Home Landing Portal Module</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Multi-Sport Tournaments Module</v>
+        <v>Bracket Management Module</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Tournament Management Module</v>
+        <v>Badminton Matches Module</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Member Management Module</v>
+        <v>Carrom Matches Module</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
-      </c>
-      <c r="B18" t="str">
-        <v/>
+        <v>Chess Matches Module</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
+        <v>Cricket Matches Module</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Dual Division Matches Module</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Match Arena &amp; Rounds Module</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Table Tennis Matches Module</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Multi-Sport Tournaments Module</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Notification Center Module</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Server Health &amp; Downtime Module</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Tournament Management Module</v>
+      </c>
+      <c r="B26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Member Management Module</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v/>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
         <v>How to Update</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B29" t="str">
         <v>Whenever a new Playwright test is written in tests/**/*.spec.ts, run `npm run update:test-sheet`. The script parses the TypeScript code directly and updates this workbook.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B29"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -630,6 +720,1695 @@
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
+        <v>DUAL-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Dual Division Matches</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Dual Division (Singles &amp; Doubles) Matches &amp; Championship Progression</v>
+      </c>
+      <c r="D2" t="str">
+        <v>DUAL-01: Dual Division Championship Creation - Umbrella tournament with Singles &amp; Doubles sub-tournaments and card badge</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Executes DUAL-01: Dual Division Championship Creation - Umbrella tournament with Singles &amp; Doubles sub-tournaments and card badge. Grouped verification includes: Navigate to Create Tournament page, Select Table Tennis and choose Dual Division mode, Verify unified parent tournament card displays Dual Division badge on Tournaments list.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G2" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Create Tournament page
+2. Select Table Tennis and choose Dual Division mode
+3. Verify unified parent tournament card displays Dual Division badge on Tournaments list</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Successfully completes execution: Verify unified parent tournament card displays Dual Division badge on Tournaments list without errors.</v>
+      </c>
+      <c r="J2" t="str">
+        <v>apps/tt-client/tests/matches/dual-division.spec.ts</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>DUAL-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Dual Division Matches</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Dual Division (Singles &amp; Doubles) Matches &amp; Championship Progression</v>
+      </c>
+      <c r="D3" t="str">
+        <v>DUAL-02: Division Switcher &amp; Independent Match Execution Across Both Divisions</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Executes DUAL-02: Division Switcher &amp; Independent Match Execution Across Both Divisions. Grouped verification includes: Create Dual Division tournament and open details, Verify Division Switcher is rendered with Singles and Doubles buttons, Seed and run Singles Division matches, Switch to Doubles Division, seed teams, and record doubles match, Switch back to Singles Division and confirm independent state is preserved.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G3" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create Dual Division tournament and open details
+2. Verify Division Switcher is rendered with Singles and Doubles buttons
+3. Seed and run Singles Division matches
+4. Switch to Doubles Division, seed teams, and record doubles match
+5. Switch back to Singles Division and confirm independent state is preserved</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Successfully completes execution: Switch back to Singles Division and confirm independent state is preserved without errors.</v>
+      </c>
+      <c r="J3" t="str">
+        <v>apps/tt-client/tests/matches/dual-division.spec.ts</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="45.83203125" customWidth="1"/>
+    <col min="5" max="5" width="55.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
+    <col min="9" max="9" width="45.83203125" customWidth="1"/>
+    <col min="10" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Module</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Scenario Group</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Test Type</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Automated Steps</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Expected Result</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Spec File</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Created At</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Last Updated</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>ARENA-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Match Arena &amp; Rounds</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Match Arena - Round Configuration, Live Scoring &amp; Team Registration</v>
+      </c>
+      <c r="D2" t="str">
+        <v>ARENA-01: Configure Best-of-3 rounds, initiate live match, record round-by-round results, and finalize match winner</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Executes ARENA-01: Configure Best-of-3 rounds, initiate live match, record round-by-round results, and finalize match winner. Grouped verification includes: Create tournament and generate matches, Navigate to Match Arena page from first scheduled match, Verify Match Configuration stage and select Best of 3 format, Start Match and verify transition to LIVE status, Record Round 1: Player A wins 11 - 8, Record Round 2: Player A wins 11 - 6 to clinch Best of 3 match, Finalize and record match result to advance winner.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G2" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create tournament and generate matches
+2. Navigate to Match Arena page from first scheduled match
+3. Verify Match Configuration stage and select Best of 3 format
+4. Start Match and verify transition to LIVE status
+5. Record Round 1: Player A wins 11 - 8
+6. Record Round 2: Player A wins 11 - 6 to clinch Best of 3 match
+7. Finalize and record match result to advance winner</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Successfully completes execution: Finalize and record match result to advance winner without errors.</v>
+      </c>
+      <c r="J2" t="str">
+        <v>apps/tt-client/tests/matches/match-arena.spec.ts</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2026-10-14</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>ARENA-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Match Arena &amp; Rounds</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Match Arena - Round Configuration, Live Scoring &amp; Team Registration</v>
+      </c>
+      <c r="D3" t="str">
+        <v>ARENA-02: Team registration in team tournament succeeds without GraphQL variable errors</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Executes ARENA-02: Team registration in team tournament succeeds without GraphQL variable errors. Grouped verification includes: Create a Team tournament, Open tournament and click Register Team, Fill team details with team name and submit.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G3" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create a Team tournament
+2. Open tournament and click Register Team
+3. Fill team details with team name and submit</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Successfully completes execution: Fill team details with team name and submit without errors.</v>
+      </c>
+      <c r="J3" t="str">
+        <v>apps/tt-client/tests/matches/match-arena.spec.ts</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2026-10-14</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="45.83203125" customWidth="1"/>
+    <col min="5" max="5" width="55.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
+    <col min="9" max="9" width="45.83203125" customWidth="1"/>
+    <col min="10" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Module</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Scenario Group</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Test Type</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Automated Steps</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Expected Result</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Spec File</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Created At</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Last Updated</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>TT-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Table Tennis Matches</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Table Tennis Matches &amp; Bracket Progression</v>
+      </c>
+      <c r="D2" t="str">
+        <v>TT-01: Table Tennis Singles - 4 players bracket generation, set scores entry, winner advance to final, and champion crown</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Executes TT-01: Table Tennis Singles - 4 players bracket generation, set scores entry, winner advance to final, and champion crown. Grouped verification includes: Create Table Tennis Singles tournament, Open tournament details and inspect overview, Seed 4 realistic players and verify automatic Round 1 bracket generation, Verify Round 1 matches render with two semifinal match pairings, Record scores for Semifinal Match 1 (11 - 7) and advance winner, Record scores for Semifinal Match 2 (8 - 11) and advance winner to Grand Final, Verify Grand Final match generated and record championship score (11 - 9), Verify Champion Victory Banner and final winner name.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G2" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create Table Tennis Singles tournament
+2. Open tournament details and inspect overview
+3. Seed 4 realistic players and verify automatic Round 1 bracket generation
+4. Verify Round 1 matches render with two semifinal match pairings
+5. Record scores for Semifinal Match 1 (11 - 7) and advance winner
+6. Record scores for Semifinal Match 2 (8 - 11) and advance winner to Grand Final
+7. Verify Grand Final match generated and record championship score (11 - 9)
+8. Verify Champion Victory Banner and final winner name</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Successfully completes execution: Verify Champion Victory Banner and final winner name without errors.</v>
+      </c>
+      <c r="J2" t="str">
+        <v>apps/tt-client/tests/matches/table-tennis.spec.ts</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>TT-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Table Tennis Matches</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Table Tennis Matches &amp; Bracket Progression</v>
+      </c>
+      <c r="D3" t="str">
+        <v>TT-02: Table Tennis Doubles - Team registration of 2-player pairs, Wave 1 draw, and set progression</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Executes TT-02: Table Tennis Doubles - Team registration of 2-player pairs, Wave 1 draw, and set progression. Grouped verification includes: Create Table Tennis Doubles tournament (Team mode with team size 2), Open doubles tournament and seed 2-player pairs, Verify Wave 1 team matches rendered and record pair score.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G3" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create Table Tennis Doubles tournament (Team mode with team size 2)
+2. Open doubles tournament and seed 2-player pairs
+3. Verify Wave 1 team matches rendered and record pair score</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Successfully completes execution: Verify Wave 1 team matches rendered and record pair score without errors.</v>
+      </c>
+      <c r="J3" t="str">
+        <v>apps/tt-client/tests/matches/table-tennis.spec.ts</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="45.83203125" customWidth="1"/>
+    <col min="5" max="5" width="55.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
+    <col min="9" max="9" width="45.83203125" customWidth="1"/>
+    <col min="10" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Module</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Scenario Group</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Test Type</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Automated Steps</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Expected Result</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Spec File</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Created At</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Last Updated</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>SPRT-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Multi-Sport Tournaments</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
+      </c>
+      <c r="D2" t="str">
+        <v>SPRT-01: Multi-Sport Form Adapters - sport presets auto-populate format, team limits, and rules</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Executes SPRT-01: Multi-Sport Form Adapters - sport presets auto-populate format, team limits, and rules. Grouped verification includes: Navigate to Create Tournament page, Verify default Table Tennis preset configuration, Select Cricket sport card and verify adaptive fields for team competition, Select Chess sport card and verify scoring format is GAME_POINTS, Test quick rule template chip appending and live preview tab.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G2" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Create Tournament page
+2. Verify default Table Tennis preset configuration
+3. Select Cricket sport card and verify adaptive fields for team competition
+4. Select Chess sport card and verify scoring format is GAME_POINTS
+5. Test quick rule template chip appending and live preview tab</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Successfully completes execution: Test quick rule template chip appending and live preview tab without errors.</v>
+      </c>
+      <c r="J2" t="str">
+        <v>apps/tt-client/tests/multi-sport.spec.ts</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>SPRT-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Multi-Sport Tournaments</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
+      </c>
+      <c r="D3" t="str">
+        <v>SPRT-02: Duplicate Registration Guard - prevents re-registration and displays Already Registered badge</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Executes SPRT-02: Duplicate Registration Guard - prevents re-registration and displays Already Registered badge. Grouped verification includes: Create an individual tournament, Open tournament and register current user, Verify Hero now shows Already Registered badge and register button is removed, Verify user is listed in Participants tab.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>UI / Functional</v>
+      </c>
+      <c r="G3" t="str">
+        <v>P0 (Critical)</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create an individual tournament
+2. Open tournament and register current user
+3. Verify Hero now shows Already Registered badge and register button is removed
+4. Verify user is listed in Participants tab</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Successfully completes execution: Verify user is listed in Participants tab without errors.</v>
+      </c>
+      <c r="J3" t="str">
+        <v>apps/tt-client/tests/multi-sport.spec.ts</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>SPRT-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Multi-Sport Tournaments</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
+      </c>
+      <c r="D4" t="str">
+        <v>SPRT-03: Team Sports Registration - team modal, min team size enforcement, and unique player assignment</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Executes SPRT-03: Team Sports Registration - team modal, min team size enforcement, and unique player assignment. Grouped verification includes: Create a team Cricket tournament with minTeamSize = 2, Open Cricket tournament details and click Register Team, Verify Register Team Modal opens and enforces minimum team size, Add additional member and successfully submit team.</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G4" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create a team Cricket tournament with minTeamSize = 2
+2. Open Cricket tournament details and click Register Team
+3. Verify Register Team Modal opens and enforces minimum team size
+4. Add additional member and successfully submit team</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Successfully completes execution: Add additional member and successfully submit team without errors.</v>
+      </c>
+      <c r="J4" t="str">
+        <v>apps/tt-client/tests/multi-sport.spec.ts</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M4" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>SPRT-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Multi-Sport Tournaments</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
+      </c>
+      <c r="D5" t="str">
+        <v>SPRT-04: Wave-by-Wave Progression &amp; Sport Scoring - registration lock, wave draws, sport-specific score entry, and finals crowning</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Executes SPRT-04: Wave-by-Wave Progression &amp; Sport Scoring - registration lock, wave draws, sport-specific score entry, and finals crowning. Grouped verification includes: Create tournament and navigate to matches tab, Verify registration window status is initially open, Seed 4 dummy players to populate participants, Verify matches tab renders bracket round 1 with sport-specific scoring modal triggers, Complete remaining matches and verify Grand Final champion banner.</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G5" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create tournament and navigate to matches tab
+2. Verify registration window status is initially open
+3. Seed 4 dummy players to populate participants
+4. Verify matches tab renders bracket round 1 with sport-specific scoring modal triggers
+5. Complete remaining matches and verify Grand Final champion banner</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Successfully completes execution: Complete remaining matches and verify Grand Final champion banner without errors.</v>
+      </c>
+      <c r="J5" t="str">
+        <v>apps/tt-client/tests/multi-sport.spec.ts</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L5" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M5" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>SPRT-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Multi-Sport Tournaments</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
+      </c>
+      <c r="D6" t="str">
+        <v>SPRT-06: Dual Division (Singles &amp; Doubles) - creates parent Championship with sub-tournaments, division switcher, and dual winners</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Executes SPRT-06: Dual Division (Singles &amp; Doubles) - creates parent Championship with sub-tournaments, division switcher, and dual winners. Grouped verification includes: Navigate to Create Tournament page, Select Table Tennis and choose Dual Division mode, Verify unified parent tournament card displays Dual Division badge on Tournaments list, Open Championship details and verify Division Switcher tabs exist, Switch between Singles and Doubles divisions and verify separate sub-tournaments and rosters.</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G6" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Create Tournament page
+2. Select Table Tennis and choose Dual Division mode
+3. Verify unified parent tournament card displays Dual Division badge on Tournaments list
+4. Open Championship details and verify Division Switcher tabs exist
+5. Switch between Singles and Doubles divisions and verify separate sub-tournaments and rosters</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Successfully completes execution: Switch between Singles and Doubles divisions and verify separate sub-tournaments and rosters without errors.</v>
+      </c>
+      <c r="J6" t="str">
+        <v>apps/tt-client/tests/multi-sport.spec.ts</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L6" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M6" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="45.83203125" customWidth="1"/>
+    <col min="5" max="5" width="55.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
+    <col min="9" max="9" width="45.83203125" customWidth="1"/>
+    <col min="10" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Module</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Scenario Group</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Test Type</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Automated Steps</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Expected Result</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Spec File</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Created At</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Last Updated</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>NOTIF-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Notification Center</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Notification Center &amp; Sports Alerts System</v>
+      </c>
+      <c r="D2" t="str">
+        <v>NOTIF-01: Notification Dropdown &amp; Filtering - Unread badge, dropdown toggle, and category tabs</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Executes NOTIF-01: Notification Dropdown &amp; Filtering - Unread badge, dropdown toggle, and category tabs. Grouped verification includes: Open landing page and inspect notification bell button, Click notification bell to open interactive dropdown, Verify initial dummy sports notifications rendered, Filter by Matches category and verify count, Filter by Tournaments category, Switch back to All filter tab.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>State Transition</v>
+      </c>
+      <c r="G2" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Open landing page and inspect notification bell button
+2. Click notification bell to open interactive dropdown
+3. Verify initial dummy sports notifications rendered
+4. Filter by Matches category and verify count
+5. Filter by Tournaments category
+6. Switch back to All filter tab</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Successfully completes execution: Switch back to All filter tab without errors.</v>
+      </c>
+      <c r="J2" t="str">
+        <v>apps/tt-client/tests/notifications.spec.ts</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>NOTIF-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Notification Center</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Notification Center &amp; Sports Alerts System</v>
+      </c>
+      <c r="D3" t="str">
+        <v>NOTIF-02: Notification Actions - Mark all as read and clear notifications</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Executes NOTIF-02: Notification Actions - Mark all as read and clear notifications. Grouped verification includes: Open notification center dropdown, Click Mark all as read and verify unread badge dismissed, Click Clear all notifications and verify empty state rendered, Close notifications dropdown via close button.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G3" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Open notification center dropdown
+2. Click Mark all as read and verify unread badge dismissed
+3. Click Clear all notifications and verify empty state rendered
+4. Close notifications dropdown via close button</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Successfully completes execution: Close notifications dropdown via close button without errors.</v>
+      </c>
+      <c r="J3" t="str">
+        <v>apps/tt-client/tests/notifications.spec.ts</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="45.83203125" customWidth="1"/>
+    <col min="5" max="5" width="55.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
+    <col min="9" max="9" width="45.83203125" customWidth="1"/>
+    <col min="10" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Module</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Scenario Group</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Test Type</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Automated Steps</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Expected Result</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Spec File</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Created At</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Last Updated</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>SRV-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Server Health &amp; Downtime</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Server Health &amp; Downtime Error Handling</v>
+      </c>
+      <c r="D2" t="str">
+        <v>SRV-01: Server is down Banner - Displays user-friendly error when API gateway is unreachable</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Executes SRV-01: Server is down Banner - Displays user-friendly error when API gateway is unreachable. Grouped verification includes: Navigate to landing page and observe network failure handling, Verify user-friendly Server is down banner is displayed, Verify Sidebar reflects Server Offline status, Verify Retry Connection action button exists on banner.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>UI / Functional</v>
+      </c>
+      <c r="G2" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to landing page and observe network failure handling
+2. Verify user-friendly Server is down banner is displayed
+3. Verify Sidebar reflects Server Offline status
+4. Verify Retry Connection action button exists on banner</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Successfully completes execution: Verify Retry Connection action button exists on banner without errors.</v>
+      </c>
+      <c r="J2" t="str">
+        <v>apps/tt-client/tests/server-health.spec.ts</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>SRV-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Server Health &amp; Downtime</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Server Health &amp; Downtime Error Handling</v>
+      </c>
+      <c r="D3" t="str">
+        <v>SRV-02: Server Downtime Recovery &amp; Dismissal - Dismissing banner and retry workflow</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Executes SRV-02: Server Downtime Recovery &amp; Dismissal - Dismissing banner and retry workflow. Grouped verification includes: Navigate to application and trigger server down banner, Dismiss banner via close button and verify it hides.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G3" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to application and trigger server down banner
+2. Dismiss banner via close button and verify it hides</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Successfully completes execution: Dismiss banner via close button and verify it hides without errors.</v>
+      </c>
+      <c r="J3" t="str">
+        <v>apps/tt-client/tests/server-health.spec.ts</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="45.83203125" customWidth="1"/>
+    <col min="5" max="5" width="55.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
+    <col min="9" max="9" width="45.83203125" customWidth="1"/>
+    <col min="10" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Module</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Scenario Group</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Test Type</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Automated Steps</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Expected Result</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Spec File</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Created At</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Last Updated</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>TRN-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Tournament Management</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Tournament Management CRUD &amp; Validation Operations</v>
+      </c>
+      <c r="D2" t="str">
+        <v>CREATE: should create a new tournament successfully with valid data and show in directory</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Executes CREATE: should create a new tournament successfully with valid data and show in directory. Grouped verification includes: Navigate to tournaments list, Open tournament creation form, Fill and submit tournament form with valid payload, Verify redirection back to tournaments directory, Search for created tournament and verify presence in grid.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>CRUD - Create (Positive)</v>
+      </c>
+      <c r="G2" t="str">
+        <v>P0 (Critical)</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to tournaments list
+2. Open tournament creation form
+3. Fill and submit tournament form with valid payload
+4. Verify redirection back to tournaments directory
+5. Search for created tournament and verify presence in grid</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Successfully completes execution: Search for created tournament and verify presence in grid without errors.</v>
+      </c>
+      <c r="J2" t="str">
+        <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>TRN-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Tournament Management</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Tournament Management CRUD &amp; Validation Operations</v>
+      </c>
+      <c r="D3" t="str">
+        <v>VALIDATION: should enforce client-side date &amp; length constraints on tournament creation</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Executes VALIDATION: should enforce client-side date &amp; length constraints on tournament creation. Grouped verification includes: Navigate to tournament creation page, Verify title minimum length constraint (&lt; 3 characters), Verify chronological date constraint (start date after registration deadline).</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Validation (Negative)</v>
+      </c>
+      <c r="G3" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to tournament creation page
+2. Verify title minimum length constraint (&lt; 3 characters)
+3. Verify chronological date constraint (start date after registration deadline)</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Successfully completes execution: Verify chronological date constraint (start date after registration deadline) without errors.</v>
+      </c>
+      <c r="J3" t="str">
+        <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>TRN-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Tournament Management</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Tournament Management CRUD &amp; Validation Operations</v>
+      </c>
+      <c r="D4" t="str">
+        <v>READ: should navigate to tournament details and inspect overview, participants, and tabs</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Executes READ: should navigate to tournament details and inspect overview, participants, and tabs. Grouped verification includes: Create tournament prerequisite, Search and navigate to tournament details page, Switch between tabs and verify content containers.</v>
+      </c>
+      <c r="F4" t="str">
+        <v>CRUD - Read (Positive)</v>
+      </c>
+      <c r="G4" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create tournament prerequisite
+2. Search and navigate to tournament details page
+3. Switch between tabs and verify content containers</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Successfully completes execution: Switch between tabs and verify content containers without errors.</v>
+      </c>
+      <c r="J4" t="str">
+        <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M4" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>TRN-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Tournament Management</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Tournament Management CRUD &amp; Validation Operations</v>
+      </c>
+      <c r="D5" t="str">
+        <v>UPDATE: should edit tournament details from settings tab and verify updates in real-time</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Executes UPDATE: should edit tournament details from settings tab and verify updates in real-time. Grouped verification includes: Create tournament prerequisite, Navigate to tournament details page, Update tournament settings with new fields, Verify success alert and updated hero title in real-time.</v>
+      </c>
+      <c r="F5" t="str">
+        <v>CRUD - Update (Positive)</v>
+      </c>
+      <c r="G5" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create tournament prerequisite
+2. Navigate to tournament details page
+3. Update tournament settings with new fields
+4. Verify success alert and updated hero title in real-time</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Successfully completes execution: Verify success alert and updated hero title in real-time without errors.</v>
+      </c>
+      <c r="J5" t="str">
+        <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L5" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M5" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>TRN-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Tournament Management</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Tournament Management CRUD &amp; Validation Operations</v>
+      </c>
+      <c r="D6" t="str">
+        <v>STATUS &amp; REGISTRATION: should change operational status and allow player registration</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Executes STATUS &amp; REGISTRATION: should change operational status and allow player registration. Grouped verification includes: Create tournament prerequisite, Navigate to tournament details page, Change status to ACTIVE via Settings tab, Register current authenticated user for tournament, Verify participant count incremented.</v>
+      </c>
+      <c r="F6" t="str">
+        <v>State Transition</v>
+      </c>
+      <c r="G6" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create tournament prerequisite
+2. Navigate to tournament details page
+3. Change status to ACTIVE via Settings tab
+4. Register current authenticated user for tournament
+5. Verify participant count incremented</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Successfully completes execution: Verify participant count incremented without errors.</v>
+      </c>
+      <c r="J6" t="str">
+        <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L6" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M6" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>TRN-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Tournament Management</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Tournament Management CRUD &amp; Validation Operations</v>
+      </c>
+      <c r="D7" t="str">
+        <v>DELETE: should soft-delete tournament and verify removal from directory</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Executes DELETE: should soft-delete tournament and verify removal from directory. Grouped verification includes: Create tournament prerequisite, Navigate to tournament details page, Accept confirmation dialog and delete tournament from hero, Verify redirection and tournament removed from directory.</v>
+      </c>
+      <c r="F7" t="str">
+        <v>CRUD - Delete</v>
+      </c>
+      <c r="G7" t="str">
+        <v>P0 (Critical)</v>
+      </c>
+      <c r="H7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create tournament prerequisite
+2. Navigate to tournament details page
+3. Accept confirmation dialog and delete tournament from hero
+4. Verify redirection and tournament removed from directory</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Successfully completes execution: Verify redirection and tournament removed from directory without errors.</v>
+      </c>
+      <c r="J7" t="str">
+        <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L7" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M7" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="45.83203125" customWidth="1"/>
+    <col min="5" max="5" width="55.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
+    <col min="9" max="9" width="45.83203125" customWidth="1"/>
+    <col min="10" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Module</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Scenario Group</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Test Type</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Automated Steps</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Expected Result</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Spec File</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Created At</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Last Updated</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>USER-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Member Management</v>
+      </c>
+      <c r="C2" t="str">
+        <v>User &amp; Member Management CRUD Operations</v>
+      </c>
+      <c r="D2" t="str">
+        <v>CREATE: should create a new user/member successfully and display in directory</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Executes CREATE: should create a new user/member successfully and display in directory. Grouped verification includes: Navigate to member management directory, Open user creation form, Fill and submit user creation form with DataFactory payload, Verify redirection back to member directory, Search for the newly created user and verify presence in table.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>CRUD - Create (Positive)</v>
+      </c>
+      <c r="G2" t="str">
+        <v>P0 (Critical)</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to member management directory
+2. Open user creation form
+3. Fill and submit user creation form with DataFactory payload
+4. Verify redirection back to member directory
+5. Search for the newly created user and verify presence in table</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Successfully completes execution: Search for the newly created user and verify presence in table without errors.</v>
+      </c>
+      <c r="J2" t="str">
+        <v>apps/tt-client/tests/user-crud.spec.ts</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>USER-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Member Management</v>
+      </c>
+      <c r="C3" t="str">
+        <v>User &amp; Member Management CRUD Operations</v>
+      </c>
+      <c r="D3" t="str">
+        <v>READ: should navigate to user profile and view complete details</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Executes READ: should navigate to user profile and view complete details. Grouped verification includes: Create user for profile inspection, Filter/search to locate the created user, Click user name link to navigate to details page, Verify member details page renders with matching identity.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>CRUD - Read (Positive)</v>
+      </c>
+      <c r="G3" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create user for profile inspection
+2. Filter/search to locate the created user
+3. Click user name link to navigate to details page
+4. Verify member details page renders with matching identity</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Successfully completes execution: Verify member details page renders with matching identity without errors.</v>
+      </c>
+      <c r="J3" t="str">
+        <v>apps/tt-client/tests/user-crud.spec.ts</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>USER-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Member Management</v>
+      </c>
+      <c r="C4" t="str">
+        <v>User &amp; Member Management CRUD Operations</v>
+      </c>
+      <c r="D4" t="str">
+        <v>UPDATE: should update user details (name, role, status) and verify changes</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Executes UPDATE: should update user details (name, role, status) and verify changes. Grouped verification includes: Create target user for updating, Locate user and open edit page via action dropdown, Apply updates to user details, Verify redirection to profile and updated details.</v>
+      </c>
+      <c r="F4" t="str">
+        <v>CRUD - Update (Positive)</v>
+      </c>
+      <c r="G4" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create target user for updating
+2. Locate user and open edit page via action dropdown
+3. Apply updates to user details
+4. Verify redirection to profile and updated details</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Successfully completes execution: Verify redirection to profile and updated details without errors.</v>
+      </c>
+      <c r="J4" t="str">
+        <v>apps/tt-client/tests/user-crud.spec.ts</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M4" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>USER-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Member Management</v>
+      </c>
+      <c r="C5" t="str">
+        <v>User &amp; Member Management CRUD Operations</v>
+      </c>
+      <c r="D5" t="str">
+        <v>STATUS TOGGLE: should toggle user account status between active and inactive</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Executes STATUS TOGGLE: should toggle user account status between active and inactive. Grouped verification includes: Create user for status toggling, Search for the member in directory, Open dropdown menu and toggle account status, Verify status badge updates to Inactive.</v>
+      </c>
+      <c r="F5" t="str">
+        <v>State Transition</v>
+      </c>
+      <c r="G5" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create user for status toggling
+2. Search for the member in directory
+3. Open dropdown menu and toggle account status
+4. Verify status badge updates to Inactive</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Successfully completes execution: Verify status badge updates to Inactive without errors.</v>
+      </c>
+      <c r="J5" t="str">
+        <v>apps/tt-client/tests/user-crud.spec.ts</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L5" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M5" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>USER-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Member Management</v>
+      </c>
+      <c r="C6" t="str">
+        <v>User &amp; Member Management CRUD Operations</v>
+      </c>
+      <c r="D6" t="str">
+        <v>DELETE: should soft-delete user and verify removal from directory</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Executes DELETE: should soft-delete user and verify removal from directory. Grouped verification includes: Create user to delete, Search and locate member in directory, Navigate to details page and trigger deletion with confirmation dialog, Verify redirected to /members and user is no longer listed.</v>
+      </c>
+      <c r="F6" t="str">
+        <v>CRUD - Delete</v>
+      </c>
+      <c r="G6" t="str">
+        <v>P0 (Critical)</v>
+      </c>
+      <c r="H6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create user to delete
+2. Search and locate member in directory
+3. Navigate to details page and trigger deletion with confirmation dialog
+4. Verify redirected to /members and user is no longer listed</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Successfully completes execution: Verify redirected to /members and user is no longer listed without errors.</v>
+      </c>
+      <c r="J6" t="str">
+        <v>apps/tt-client/tests/user-crud.spec.ts</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L6" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M6" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M49"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="45.83203125" customWidth="1"/>
+    <col min="5" max="5" width="55.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
+    <col min="9" max="9" width="45.83203125" customWidth="1"/>
+    <col min="10" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Module</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Scenario Group</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Test Type</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Automated Steps</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Expected Result</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Spec File</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Created At</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Last Updated</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
         <v>AUTH-001</v>
       </c>
       <c r="B2" t="str">
@@ -1054,19 +2833,19 @@
     </row>
     <row r="12" xml:space="preserve">
       <c r="A12" t="str">
-        <v>BRKT-001</v>
+        <v>HOME-001</v>
       </c>
       <c r="B12" t="str">
-        <v>Bracket Management</v>
+        <v>Home Landing Portal</v>
       </c>
       <c r="C12" t="str">
-        <v>Tournament Match Generation, Bracket Progression &amp; Winner Finalization</v>
+        <v>Home Landing Page &amp; Public Information Portal</v>
       </c>
       <c r="D12" t="str">
-        <v>BRACKET E2E: should seed dummy players, randomly generate Round 1 matches, progress winners to Final, and crown Tournament Champion</v>
+        <v>HOME-01: Public Landing Access - Unauthenticated guest can view Home page with hero, live stats, and sport categories</v>
       </c>
       <c r="E12" t="str">
-        <v>Executes BRACKET E2E: should seed dummy players, randomly generate Round 1 matches, progress winners to Final, and crown Tournament Champion. Grouped verification includes: Create a new 4-player knockout tournament, Open tournament details and switch to Matches tab, Seed 4 dummy players and verify Round 1 Semifinals matches are randomly generated, Validate edge case: reject tied score in knockout match, Record Round 1 Match #1 result and verify Winner advances to newly registered Grand Final match, Record Round 1 Match #2 result and verify Grand Final becomes SCHEDULED with both finalists, Record Grand Final result and verify Official Tournament Champion is crowned, Verify Home Dashboard displays the Latest Tournament with Champion and global Matches page lists all matches.</v>
+        <v>Executes HOME-01: Public Landing Access - Unauthenticated guest can view Home page with hero, live stats, and sport categories. Grouped verification includes: Navigate to root path as guest and verify no redirect to login, Verify Topbar renders guest navigation controls, Verify Home Hero banner and live sports platform headline, Verify multi-sport categories showcase contains all supported sports, Click sport category filter and verify active button state.</v>
       </c>
       <c r="F12" t="str">
         <v>Functional E2E</v>
@@ -1075,6 +2854,95 @@
         <v>P1 (High)</v>
       </c>
       <c r="H12" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to root path as guest and verify no redirect to login
+2. Verify Topbar renders guest navigation controls
+3. Verify Home Hero banner and live sports platform headline
+4. Verify multi-sport categories showcase contains all supported sports
+5. Click sport category filter and verify active button state</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Successfully completes execution: Click sport category filter and verify active button state without errors.</v>
+      </c>
+      <c r="J12" t="str">
+        <v>apps/tt-client/tests/home.spec.ts</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L12" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M12" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>HOME-002</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Home Landing Portal</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Home Landing Page &amp; Public Information Portal</v>
+      </c>
+      <c r="D13" t="str">
+        <v>HOME-02: Authenticated Experience - Seamless transition with personalized topbar and sidebar navigation</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Executes HOME-02: Authenticated Experience - Seamless transition with personalized topbar and sidebar navigation. Grouped verification includes: Authenticate seeded player session, Navigate to Home via Sidebar navigation, Verify authenticated Topbar displays user greeting and sign out action, Verify Featured Latest Tournament and Current Match cards exist.</v>
+      </c>
+      <c r="F13" t="str">
+        <v>State Transition</v>
+      </c>
+      <c r="G13" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H13" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Authenticate seeded player session
+2. Navigate to Home via Sidebar navigation
+3. Verify authenticated Topbar displays user greeting and sign out action
+4. Verify Featured Latest Tournament and Current Match cards exist</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Successfully completes execution: Verify Featured Latest Tournament and Current Match cards exist without errors.</v>
+      </c>
+      <c r="J13" t="str">
+        <v>apps/tt-client/tests/home.spec.ts</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L13" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M13" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>BRKT-001</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Bracket Management</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Tournament Match Generation, Bracket Progression &amp; Winner Finalization</v>
+      </c>
+      <c r="D14" t="str">
+        <v>BRACKET E2E: should seed dummy players, randomly generate Round 1 matches, progress winners to Final, and crown Tournament Champion</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Executes BRACKET E2E: should seed dummy players, randomly generate Round 1 matches, progress winners to Final, and crown Tournament Champion. Grouped verification includes: Create a new 4-player knockout tournament, Open tournament details and switch to Matches tab, Seed 4 dummy players and verify Round 1 Semifinals matches are randomly generated, Validate edge case: reject tied score in knockout match, Record Round 1 Match #1 result and verify Winner advances to newly registered Grand Final match, Record Round 1 Match #2 result and verify Grand Final becomes SCHEDULED with both finalists, Record Grand Final result and verify Official Tournament Champion is crowned, Verify Home Dashboard displays the Latest Tournament with Champion and global Matches page lists all matches.</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G14" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H14" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create a new 4-player knockout tournament
 2. Open tournament details and switch to Matches tab
 3. Seed 4 dummy players and verify Round 1 Semifinals matches are randomly generated
@@ -1084,688 +2952,1571 @@
 7. Record Grand Final result and verify Official Tournament Champion is crowned
 8. Verify Home Dashboard displays the Latest Tournament with Champion and global Matches page lists all matches</v>
       </c>
-      <c r="I12" t="str">
+      <c r="I14" t="str">
         <v>Successfully completes execution: Verify Home Dashboard displays the Latest Tournament with Champion and global Matches page lists all matches without errors.</v>
       </c>
-      <c r="J12" t="str">
+      <c r="J14" t="str">
         <v>apps/tt-client/tests/match-bracket.spec.ts</v>
       </c>
-      <c r="K12" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L12" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M12" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="13" xml:space="preserve">
-      <c r="A13" t="str">
+      <c r="K14" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L14" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M14" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>BDMT-001</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Badminton Matches</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Badminton Matches &amp; Sets Progression</v>
+      </c>
+      <c r="D15" t="str">
+        <v>BDMT-01: Badminton Tournament Setup - Best of 3 sets to 21 points preset</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Executes BDMT-01: Badminton Tournament Setup - Best of 3 sets to 21 points preset. Grouped verification includes: Select Badminton sport card and verify 21-points set scoring configuration, Fill form details and submit Badminton tournament, Verify Badminton card appears on Tournaments listing.</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G15" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H15" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Select Badminton sport card and verify 21-points set scoring configuration
+2. Fill form details and submit Badminton tournament
+3. Verify Badminton card appears on Tournaments listing</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Successfully completes execution: Verify Badminton card appears on Tournaments listing without errors.</v>
+      </c>
+      <c r="J15" t="str">
+        <v>apps/tt-client/tests/matches/badminton.spec.ts</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L15" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M15" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>BDMT-002</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Badminton Matches</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Badminton Matches &amp; Sets Progression</v>
+      </c>
+      <c r="D16" t="str">
+        <v>BDMT-02: Badminton Match Play - Bracket match draw, set score entry, and finals champion</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Executes BDMT-02: Badminton Match Play - Bracket match draw, set score entry, and finals champion. Grouped verification includes: Create Badminton tournament and open details, Seed 4 badminton players and generate opening knockout matches, Record 21-points set score for Semifinal Match 1 (21 - 17), Record 21-points set score for Semifinal Match 2 (18 - 21), Record Grand Final score (21 - 19) and verify championship crown.</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G16" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H16" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create Badminton tournament and open details
+2. Seed 4 badminton players and generate opening knockout matches
+3. Record 21-points set score for Semifinal Match 1 (21 - 17)
+4. Record 21-points set score for Semifinal Match 2 (18 - 21)
+5. Record Grand Final score (21 - 19) and verify championship crown</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Successfully completes execution: Record Grand Final score (21 - 19) and verify championship crown without errors.</v>
+      </c>
+      <c r="J16" t="str">
+        <v>apps/tt-client/tests/matches/badminton.spec.ts</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L16" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M16" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>CRRM-001</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Carrom Matches</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Carrom Board Matches &amp; Points Progression</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CRRM-01: Carrom Board Tournament Setup - Auto-populates 25 points rule preset</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Executes CRRM-01: Carrom Board Tournament Setup - Auto-populates 25 points rule preset. Grouped verification includes: Select Carrom sport preset and verify rules and points configuration, Submit Carrom tournament form, Verify tournament card in directory.</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G17" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H17" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Select Carrom sport preset and verify rules and points configuration
+2. Submit Carrom tournament form
+3. Verify tournament card in directory</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Successfully completes execution: Verify tournament card in directory without errors.</v>
+      </c>
+      <c r="J17" t="str">
+        <v>apps/tt-client/tests/matches/carrom.spec.ts</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L17" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M17" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>CRRM-002</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Carrom Matches</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Carrom Board Matches &amp; Points Progression</v>
+      </c>
+      <c r="D18" t="str">
+        <v>CRRM-02: Carrom Match Fixtures &amp; Point Scoring to 25 with Queen bonus</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Executes CRRM-02: Carrom Match Fixtures &amp; Point Scoring to 25 with Queen bonus. Grouped verification includes: Create Carrom tournament and open details, Seed 4 carrom players and generate Round 1 board fixtures, Submit board points (25 - 18) for first semifinal board match, Submit board points for second match and advance to Grand Final, Submit final board score (25 - 21) and crown Carrom Champion.</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G18" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H18" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create Carrom tournament and open details
+2. Seed 4 carrom players and generate Round 1 board fixtures
+3. Submit board points (25 - 18) for first semifinal board match
+4. Submit board points for second match and advance to Grand Final
+5. Submit final board score (25 - 21) and crown Carrom Champion</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Successfully completes execution: Submit final board score (25 - 21) and crown Carrom Champion without errors.</v>
+      </c>
+      <c r="J18" t="str">
+        <v>apps/tt-client/tests/matches/carrom.spec.ts</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L18" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M18" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>CHSS-001</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Chess Matches</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Chess Duels &amp; FIDE Points Progression</v>
+      </c>
+      <c r="D19" t="str">
+        <v>CHSS-01: Chess Rapid Tournament Setup - Enforces Individual mode and GAME_POINTS scoring</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Executes CHSS-01: Chess Rapid Tournament Setup - Enforces Individual mode and GAME_POINTS scoring. Grouped verification includes: Select Chess sport card and verify individual duel mode, Submit Chess tournament form, Verify Chess tournament appears in tournament directory.</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G19" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H19" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Select Chess sport card and verify individual duel mode
+2. Submit Chess tournament form
+3. Verify Chess tournament appears in tournament directory</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Successfully completes execution: Verify Chess tournament appears in tournament directory without errors.</v>
+      </c>
+      <c r="J19" t="str">
+        <v>apps/tt-client/tests/matches/chess.spec.ts</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L19" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M19" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>CHSS-002</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Chess Matches</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Chess Duels &amp; FIDE Points Progression</v>
+      </c>
+      <c r="D20" t="str">
+        <v>CHSS-02: Chess Duel Progression - Match draw, 1.0 vs 0.0 scoring, and championship crowning</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Executes CHSS-02: Chess Duel Progression - Match draw, 1.0 vs 0.0 scoring, and championship crowning. Grouped verification includes: Create Chess tournament and open details, Seed 4 chess players and generate opening duel fixtures, Submit game point results for semifinal duels (1 - 0), Submit Grand Final game result and crown Chess Champion.</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G20" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H20" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create Chess tournament and open details
+2. Seed 4 chess players and generate opening duel fixtures
+3. Submit game point results for semifinal duels (1 - 0)
+4. Submit Grand Final game result and crown Chess Champion</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Successfully completes execution: Submit Grand Final game result and crown Chess Champion without errors.</v>
+      </c>
+      <c r="J20" t="str">
+        <v>apps/tt-client/tests/matches/chess.spec.ts</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L20" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M20" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>CRKT-001</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Cricket Matches</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Cricket Matches &amp; Squad Progression</v>
+      </c>
+      <c r="D21" t="str">
+        <v>CRKT-01: Cricket Squad Tournament Creation - Validates squad requirements and limited overs format</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Executes CRKT-01: Cricket Squad Tournament Creation - Validates squad requirements and limited overs format. Grouped verification includes: Navigate to Create Tournament page and select Cricket sport card, Verify team mode and squad limits adapt automatically, Fill schedule details and submit Cricket tournament, Verify Cricket tournament card appears on Tournaments list.</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G21" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H21" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Create Tournament page and select Cricket sport card
+2. Verify team mode and squad limits adapt automatically
+3. Fill schedule details and submit Cricket tournament
+4. Verify Cricket tournament card appears on Tournaments list</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Successfully completes execution: Verify Cricket tournament card appears on Tournaments list without errors.</v>
+      </c>
+      <c r="J21" t="str">
+        <v>apps/tt-client/tests/matches/cricket.spec.ts</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L21" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M21" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>CRKT-002</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Cricket Matches</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Cricket Matches &amp; Squad Progression</v>
+      </c>
+      <c r="D22" t="str">
+        <v>CRKT-02: Cricket Team Registration &amp; Captain Nomination</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Executes CRKT-02: Cricket Team Registration &amp; Captain Nomination. Grouped verification includes: Create Cricket squad tournament with min team size 2, Open Cricket tournament details page, Trigger Team Registration modal and register Team Titan, Inspect registered teams list on Participants tab.</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G22" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H22" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create Cricket squad tournament with min team size 2
+2. Open Cricket tournament details page
+3. Trigger Team Registration modal and register Team Titan
+4. Inspect registered teams list on Participants tab</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Successfully completes execution: Inspect registered teams list on Participants tab without errors.</v>
+      </c>
+      <c r="J22" t="str">
+        <v>apps/tt-client/tests/matches/cricket.spec.ts</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L22" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M22" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>CRKT-003</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Cricket Matches</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Cricket Matches &amp; Squad Progression</v>
+      </c>
+      <c r="D23" t="str">
+        <v>CRKT-03: Cricket Wave 1 Fixtures &amp; Limited Overs Scoring</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Executes CRKT-03: Cricket Wave 1 Fixtures &amp; Limited Overs Scoring. Grouped verification includes: Create Cricket tournament and seed squad teams, Verify Wave 1 cricket fixture and submit limited overs run score.</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G23" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H23" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create Cricket tournament and seed squad teams
+2. Verify Wave 1 cricket fixture and submit limited overs run score</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Successfully completes execution: Verify Wave 1 cricket fixture and submit limited overs run score without errors.</v>
+      </c>
+      <c r="J23" t="str">
+        <v>apps/tt-client/tests/matches/cricket.spec.ts</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L23" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M23" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>DUAL-001</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Dual Division Matches</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Dual Division (Singles &amp; Doubles) Matches &amp; Championship Progression</v>
+      </c>
+      <c r="D24" t="str">
+        <v>DUAL-01: Dual Division Championship Creation - Umbrella tournament with Singles &amp; Doubles sub-tournaments and card badge</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Executes DUAL-01: Dual Division Championship Creation - Umbrella tournament with Singles &amp; Doubles sub-tournaments and card badge. Grouped verification includes: Navigate to Create Tournament page, Select Table Tennis and choose Dual Division mode, Verify unified parent tournament card displays Dual Division badge on Tournaments list.</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G24" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H24" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Create Tournament page
+2. Select Table Tennis and choose Dual Division mode
+3. Verify unified parent tournament card displays Dual Division badge on Tournaments list</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Successfully completes execution: Verify unified parent tournament card displays Dual Division badge on Tournaments list without errors.</v>
+      </c>
+      <c r="J24" t="str">
+        <v>apps/tt-client/tests/matches/dual-division.spec.ts</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L24" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M24" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>DUAL-002</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Dual Division Matches</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Dual Division (Singles &amp; Doubles) Matches &amp; Championship Progression</v>
+      </c>
+      <c r="D25" t="str">
+        <v>DUAL-02: Division Switcher &amp; Independent Match Execution Across Both Divisions</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Executes DUAL-02: Division Switcher &amp; Independent Match Execution Across Both Divisions. Grouped verification includes: Create Dual Division tournament and open details, Verify Division Switcher is rendered with Singles and Doubles buttons, Seed and run Singles Division matches, Switch to Doubles Division, seed teams, and record doubles match, Switch back to Singles Division and confirm independent state is preserved.</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G25" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H25" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create Dual Division tournament and open details
+2. Verify Division Switcher is rendered with Singles and Doubles buttons
+3. Seed and run Singles Division matches
+4. Switch to Doubles Division, seed teams, and record doubles match
+5. Switch back to Singles Division and confirm independent state is preserved</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Successfully completes execution: Switch back to Singles Division and confirm independent state is preserved without errors.</v>
+      </c>
+      <c r="J25" t="str">
+        <v>apps/tt-client/tests/matches/dual-division.spec.ts</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L25" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M25" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>ARENA-001</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Match Arena &amp; Rounds</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Match Arena - Round Configuration, Live Scoring &amp; Team Registration</v>
+      </c>
+      <c r="D26" t="str">
+        <v>ARENA-01: Configure Best-of-3 rounds, initiate live match, record round-by-round results, and finalize match winner</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Executes ARENA-01: Configure Best-of-3 rounds, initiate live match, record round-by-round results, and finalize match winner. Grouped verification includes: Create tournament and generate matches, Navigate to Match Arena page from first scheduled match, Verify Match Configuration stage and select Best of 3 format, Start Match and verify transition to LIVE status, Record Round 1: Player A wins 11 - 8, Record Round 2: Player A wins 11 - 6 to clinch Best of 3 match, Finalize and record match result to advance winner.</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G26" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H26" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create tournament and generate matches
+2. Navigate to Match Arena page from first scheduled match
+3. Verify Match Configuration stage and select Best of 3 format
+4. Start Match and verify transition to LIVE status
+5. Record Round 1: Player A wins 11 - 8
+6. Record Round 2: Player A wins 11 - 6 to clinch Best of 3 match
+7. Finalize and record match result to advance winner</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Successfully completes execution: Finalize and record match result to advance winner without errors.</v>
+      </c>
+      <c r="J26" t="str">
+        <v>apps/tt-client/tests/matches/match-arena.spec.ts</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L26" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="M26" t="str">
+        <v>2026-10-14</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>ARENA-002</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Match Arena &amp; Rounds</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Match Arena - Round Configuration, Live Scoring &amp; Team Registration</v>
+      </c>
+      <c r="D27" t="str">
+        <v>ARENA-02: Team registration in team tournament succeeds without GraphQL variable errors</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Executes ARENA-02: Team registration in team tournament succeeds without GraphQL variable errors. Grouped verification includes: Create a Team tournament, Open tournament and click Register Team, Fill team details with team name and submit.</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G27" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H27" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create a Team tournament
+2. Open tournament and click Register Team
+3. Fill team details with team name and submit</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Successfully completes execution: Fill team details with team name and submit without errors.</v>
+      </c>
+      <c r="J27" t="str">
+        <v>apps/tt-client/tests/matches/match-arena.spec.ts</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L27" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="M27" t="str">
+        <v>2026-10-14</v>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>TT-001</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Table Tennis Matches</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Table Tennis Matches &amp; Bracket Progression</v>
+      </c>
+      <c r="D28" t="str">
+        <v>TT-01: Table Tennis Singles - 4 players bracket generation, set scores entry, winner advance to final, and champion crown</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Executes TT-01: Table Tennis Singles - 4 players bracket generation, set scores entry, winner advance to final, and champion crown. Grouped verification includes: Create Table Tennis Singles tournament, Open tournament details and inspect overview, Seed 4 realistic players and verify automatic Round 1 bracket generation, Verify Round 1 matches render with two semifinal match pairings, Record scores for Semifinal Match 1 (11 - 7) and advance winner, Record scores for Semifinal Match 2 (8 - 11) and advance winner to Grand Final, Verify Grand Final match generated and record championship score (11 - 9), Verify Champion Victory Banner and final winner name.</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G28" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H28" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create Table Tennis Singles tournament
+2. Open tournament details and inspect overview
+3. Seed 4 realistic players and verify automatic Round 1 bracket generation
+4. Verify Round 1 matches render with two semifinal match pairings
+5. Record scores for Semifinal Match 1 (11 - 7) and advance winner
+6. Record scores for Semifinal Match 2 (8 - 11) and advance winner to Grand Final
+7. Verify Grand Final match generated and record championship score (11 - 9)
+8. Verify Champion Victory Banner and final winner name</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Successfully completes execution: Verify Champion Victory Banner and final winner name without errors.</v>
+      </c>
+      <c r="J28" t="str">
+        <v>apps/tt-client/tests/matches/table-tennis.spec.ts</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L28" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M28" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>TT-002</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Table Tennis Matches</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Table Tennis Matches &amp; Bracket Progression</v>
+      </c>
+      <c r="D29" t="str">
+        <v>TT-02: Table Tennis Doubles - Team registration of 2-player pairs, Wave 1 draw, and set progression</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Executes TT-02: Table Tennis Doubles - Team registration of 2-player pairs, Wave 1 draw, and set progression. Grouped verification includes: Create Table Tennis Doubles tournament (Team mode with team size 2), Open doubles tournament and seed 2-player pairs, Verify Wave 1 team matches rendered and record pair score.</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G29" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H29" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create Table Tennis Doubles tournament (Team mode with team size 2)
+2. Open doubles tournament and seed 2-player pairs
+3. Verify Wave 1 team matches rendered and record pair score</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Successfully completes execution: Verify Wave 1 team matches rendered and record pair score without errors.</v>
+      </c>
+      <c r="J29" t="str">
+        <v>apps/tt-client/tests/matches/table-tennis.spec.ts</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L29" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M29" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
         <v>SPRT-001</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B30" t="str">
         <v>Multi-Sport Tournaments</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C30" t="str">
         <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D30" t="str">
         <v>SPRT-01: Multi-Sport Form Adapters - sport presets auto-populate format, team limits, and rules</v>
       </c>
-      <c r="E13" t="str">
+      <c r="E30" t="str">
         <v>Executes SPRT-01: Multi-Sport Form Adapters - sport presets auto-populate format, team limits, and rules. Grouped verification includes: Navigate to Create Tournament page, Verify default Table Tennis preset configuration, Select Cricket sport card and verify adaptive fields for team competition, Select Chess sport card and verify scoring format is GAME_POINTS, Test quick rule template chip appending and live preview tab.</v>
       </c>
-      <c r="F13" t="str">
+      <c r="F30" t="str">
         <v>Functional E2E</v>
       </c>
-      <c r="G13" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H13" t="str" xml:space="preserve">
+      <c r="G30" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H30" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to Create Tournament page
 2. Verify default Table Tennis preset configuration
 3. Select Cricket sport card and verify adaptive fields for team competition
 4. Select Chess sport card and verify scoring format is GAME_POINTS
 5. Test quick rule template chip appending and live preview tab</v>
       </c>
-      <c r="I13" t="str">
+      <c r="I30" t="str">
         <v>Successfully completes execution: Test quick rule template chip appending and live preview tab without errors.</v>
       </c>
-      <c r="J13" t="str">
+      <c r="J30" t="str">
         <v>apps/tt-client/tests/multi-sport.spec.ts</v>
       </c>
-      <c r="K13" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L13" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M13" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14" t="str">
+      <c r="K30" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L30" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M30" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
         <v>SPRT-002</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B31" t="str">
         <v>Multi-Sport Tournaments</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C31" t="str">
         <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D31" t="str">
         <v>SPRT-02: Duplicate Registration Guard - prevents re-registration and displays Already Registered badge</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E31" t="str">
         <v>Executes SPRT-02: Duplicate Registration Guard - prevents re-registration and displays Already Registered badge. Grouped verification includes: Create an individual tournament, Open tournament and register current user, Verify Hero now shows Already Registered badge and register button is removed, Verify user is listed in Participants tab.</v>
       </c>
-      <c r="F14" t="str">
+      <c r="F31" t="str">
         <v>UI / Functional</v>
       </c>
-      <c r="G14" t="str">
+      <c r="G31" t="str">
         <v>P0 (Critical)</v>
       </c>
-      <c r="H14" t="str" xml:space="preserve">
+      <c r="H31" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create an individual tournament
 2. Open tournament and register current user
 3. Verify Hero now shows Already Registered badge and register button is removed
 4. Verify user is listed in Participants tab</v>
       </c>
-      <c r="I14" t="str">
+      <c r="I31" t="str">
         <v>Successfully completes execution: Verify user is listed in Participants tab without errors.</v>
       </c>
-      <c r="J14" t="str">
+      <c r="J31" t="str">
         <v>apps/tt-client/tests/multi-sport.spec.ts</v>
       </c>
-      <c r="K14" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L14" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M14" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15" t="str">
+      <c r="K31" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L31" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M31" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
         <v>SPRT-003</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B32" t="str">
         <v>Multi-Sport Tournaments</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C32" t="str">
         <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
       </c>
-      <c r="D15" t="str">
+      <c r="D32" t="str">
         <v>SPRT-03: Team Sports Registration - team modal, min team size enforcement, and unique player assignment</v>
       </c>
-      <c r="E15" t="str">
+      <c r="E32" t="str">
         <v>Executes SPRT-03: Team Sports Registration - team modal, min team size enforcement, and unique player assignment. Grouped verification includes: Create a team Cricket tournament with minTeamSize = 2, Open Cricket tournament details and click Register Team, Verify Register Team Modal opens and enforces minimum team size, Add additional member and successfully submit team.</v>
       </c>
-      <c r="F15" t="str">
+      <c r="F32" t="str">
         <v>Functional E2E</v>
       </c>
-      <c r="G15" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H15" t="str" xml:space="preserve">
+      <c r="G32" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H32" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create a team Cricket tournament with minTeamSize = 2
 2. Open Cricket tournament details and click Register Team
 3. Verify Register Team Modal opens and enforces minimum team size
 4. Add additional member and successfully submit team</v>
       </c>
-      <c r="I15" t="str">
+      <c r="I32" t="str">
         <v>Successfully completes execution: Add additional member and successfully submit team without errors.</v>
       </c>
-      <c r="J15" t="str">
+      <c r="J32" t="str">
         <v>apps/tt-client/tests/multi-sport.spec.ts</v>
       </c>
-      <c r="K15" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L15" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M15" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16" t="str">
+      <c r="K32" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L32" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M32" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
         <v>SPRT-004</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B33" t="str">
         <v>Multi-Sport Tournaments</v>
       </c>
-      <c r="C16" t="str">
+      <c r="C33" t="str">
         <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
       </c>
-      <c r="D16" t="str">
+      <c r="D33" t="str">
         <v>SPRT-04: Wave-by-Wave Progression &amp; Sport Scoring - registration lock, wave draws, sport-specific score entry, and finals crowning</v>
       </c>
-      <c r="E16" t="str">
+      <c r="E33" t="str">
         <v>Executes SPRT-04: Wave-by-Wave Progression &amp; Sport Scoring - registration lock, wave draws, sport-specific score entry, and finals crowning. Grouped verification includes: Create tournament and navigate to matches tab, Verify registration window status is initially open, Seed 4 dummy players to populate participants, Verify matches tab renders bracket round 1 with sport-specific scoring modal triggers, Complete remaining matches and verify Grand Final champion banner.</v>
       </c>
-      <c r="F16" t="str">
+      <c r="F33" t="str">
         <v>Functional E2E</v>
       </c>
-      <c r="G16" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H16" t="str" xml:space="preserve">
+      <c r="G33" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H33" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create tournament and navigate to matches tab
 2. Verify registration window status is initially open
 3. Seed 4 dummy players to populate participants
 4. Verify matches tab renders bracket round 1 with sport-specific scoring modal triggers
 5. Complete remaining matches and verify Grand Final champion banner</v>
       </c>
-      <c r="I16" t="str">
+      <c r="I33" t="str">
         <v>Successfully completes execution: Complete remaining matches and verify Grand Final champion banner without errors.</v>
       </c>
-      <c r="J16" t="str">
+      <c r="J33" t="str">
         <v>apps/tt-client/tests/multi-sport.spec.ts</v>
       </c>
-      <c r="K16" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L16" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M16" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17" t="str">
+      <c r="K33" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L33" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M33" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>SPRT-005</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Multi-Sport Tournaments</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
+      </c>
+      <c r="D34" t="str">
+        <v>SPRT-06: Dual Division (Singles &amp; Doubles) - creates parent Championship with sub-tournaments, division switcher, and dual winners</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Executes SPRT-06: Dual Division (Singles &amp; Doubles) - creates parent Championship with sub-tournaments, division switcher, and dual winners. Grouped verification includes: Navigate to Create Tournament page, Select Table Tennis and choose Dual Division mode, Verify unified parent tournament card displays Dual Division badge on Tournaments list, Open Championship details and verify Division Switcher tabs exist, Switch between Singles and Doubles divisions and verify separate sub-tournaments and rosters.</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G34" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H34" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Create Tournament page
+2. Select Table Tennis and choose Dual Division mode
+3. Verify unified parent tournament card displays Dual Division badge on Tournaments list
+4. Open Championship details and verify Division Switcher tabs exist
+5. Switch between Singles and Doubles divisions and verify separate sub-tournaments and rosters</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Successfully completes execution: Switch between Singles and Doubles divisions and verify separate sub-tournaments and rosters without errors.</v>
+      </c>
+      <c r="J34" t="str">
+        <v>apps/tt-client/tests/multi-sport.spec.ts</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L34" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M34" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>NOTIF-001</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Notification Center</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Notification Center &amp; Sports Alerts System</v>
+      </c>
+      <c r="D35" t="str">
+        <v>NOTIF-01: Notification Dropdown &amp; Filtering - Unread badge, dropdown toggle, and category tabs</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Executes NOTIF-01: Notification Dropdown &amp; Filtering - Unread badge, dropdown toggle, and category tabs. Grouped verification includes: Open landing page and inspect notification bell button, Click notification bell to open interactive dropdown, Verify initial dummy sports notifications rendered, Filter by Matches category and verify count, Filter by Tournaments category, Switch back to All filter tab.</v>
+      </c>
+      <c r="F35" t="str">
+        <v>State Transition</v>
+      </c>
+      <c r="G35" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H35" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Open landing page and inspect notification bell button
+2. Click notification bell to open interactive dropdown
+3. Verify initial dummy sports notifications rendered
+4. Filter by Matches category and verify count
+5. Filter by Tournaments category
+6. Switch back to All filter tab</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Successfully completes execution: Switch back to All filter tab without errors.</v>
+      </c>
+      <c r="J35" t="str">
+        <v>apps/tt-client/tests/notifications.spec.ts</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L35" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M35" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>NOTIF-002</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Notification Center</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Notification Center &amp; Sports Alerts System</v>
+      </c>
+      <c r="D36" t="str">
+        <v>NOTIF-02: Notification Actions - Mark all as read and clear notifications</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Executes NOTIF-02: Notification Actions - Mark all as read and clear notifications. Grouped verification includes: Open notification center dropdown, Click Mark all as read and verify unread badge dismissed, Click Clear all notifications and verify empty state rendered, Close notifications dropdown via close button.</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G36" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H36" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Open notification center dropdown
+2. Click Mark all as read and verify unread badge dismissed
+3. Click Clear all notifications and verify empty state rendered
+4. Close notifications dropdown via close button</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Successfully completes execution: Close notifications dropdown via close button without errors.</v>
+      </c>
+      <c r="J36" t="str">
+        <v>apps/tt-client/tests/notifications.spec.ts</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L36" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M36" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>SRV-001</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Server Health &amp; Downtime</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Server Health &amp; Downtime Error Handling</v>
+      </c>
+      <c r="D37" t="str">
+        <v>SRV-01: Server is down Banner - Displays user-friendly error when API gateway is unreachable</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Executes SRV-01: Server is down Banner - Displays user-friendly error when API gateway is unreachable. Grouped verification includes: Navigate to landing page and observe network failure handling, Verify user-friendly Server is down banner is displayed, Verify Sidebar reflects Server Offline status, Verify Retry Connection action button exists on banner.</v>
+      </c>
+      <c r="F37" t="str">
+        <v>UI / Functional</v>
+      </c>
+      <c r="G37" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H37" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to landing page and observe network failure handling
+2. Verify user-friendly Server is down banner is displayed
+3. Verify Sidebar reflects Server Offline status
+4. Verify Retry Connection action button exists on banner</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Successfully completes execution: Verify Retry Connection action button exists on banner without errors.</v>
+      </c>
+      <c r="J37" t="str">
+        <v>apps/tt-client/tests/server-health.spec.ts</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L37" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M37" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>SRV-002</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Server Health &amp; Downtime</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Server Health &amp; Downtime Error Handling</v>
+      </c>
+      <c r="D38" t="str">
+        <v>SRV-02: Server Downtime Recovery &amp; Dismissal - Dismissing banner and retry workflow</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Executes SRV-02: Server Downtime Recovery &amp; Dismissal - Dismissing banner and retry workflow. Grouped verification includes: Navigate to application and trigger server down banner, Dismiss banner via close button and verify it hides.</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G38" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H38" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to application and trigger server down banner
+2. Dismiss banner via close button and verify it hides</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Successfully completes execution: Dismiss banner via close button and verify it hides without errors.</v>
+      </c>
+      <c r="J38" t="str">
+        <v>apps/tt-client/tests/server-health.spec.ts</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L38" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M38" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
         <v>TRN-001</v>
       </c>
-      <c r="B17" t="str">
+      <c r="B39" t="str">
         <v>Tournament Management</v>
       </c>
-      <c r="C17" t="str">
+      <c r="C39" t="str">
         <v>Tournament Management CRUD &amp; Validation Operations</v>
       </c>
-      <c r="D17" t="str">
+      <c r="D39" t="str">
         <v>CREATE: should create a new tournament successfully with valid data and show in directory</v>
       </c>
-      <c r="E17" t="str">
+      <c r="E39" t="str">
         <v>Executes CREATE: should create a new tournament successfully with valid data and show in directory. Grouped verification includes: Navigate to tournaments list, Open tournament creation form, Fill and submit tournament form with valid payload, Verify redirection back to tournaments directory, Search for created tournament and verify presence in grid.</v>
       </c>
-      <c r="F17" t="str">
+      <c r="F39" t="str">
         <v>CRUD - Create (Positive)</v>
       </c>
-      <c r="G17" t="str">
+      <c r="G39" t="str">
         <v>P0 (Critical)</v>
       </c>
-      <c r="H17" t="str" xml:space="preserve">
+      <c r="H39" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to tournaments list
 2. Open tournament creation form
 3. Fill and submit tournament form with valid payload
 4. Verify redirection back to tournaments directory
 5. Search for created tournament and verify presence in grid</v>
       </c>
-      <c r="I17" t="str">
+      <c r="I39" t="str">
         <v>Successfully completes execution: Search for created tournament and verify presence in grid without errors.</v>
       </c>
-      <c r="J17" t="str">
+      <c r="J39" t="str">
         <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
       </c>
-      <c r="K17" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L17" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M17" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="18" xml:space="preserve">
-      <c r="A18" t="str">
+      <c r="K39" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L39" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M39" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
         <v>TRN-002</v>
       </c>
-      <c r="B18" t="str">
+      <c r="B40" t="str">
         <v>Tournament Management</v>
       </c>
-      <c r="C18" t="str">
+      <c r="C40" t="str">
         <v>Tournament Management CRUD &amp; Validation Operations</v>
       </c>
-      <c r="D18" t="str">
+      <c r="D40" t="str">
         <v>VALIDATION: should enforce client-side date &amp; length constraints on tournament creation</v>
       </c>
-      <c r="E18" t="str">
+      <c r="E40" t="str">
         <v>Executes VALIDATION: should enforce client-side date &amp; length constraints on tournament creation. Grouped verification includes: Navigate to tournament creation page, Verify title minimum length constraint (&lt; 3 characters), Verify chronological date constraint (start date after registration deadline).</v>
       </c>
-      <c r="F18" t="str">
+      <c r="F40" t="str">
         <v>Validation (Negative)</v>
       </c>
-      <c r="G18" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H18" t="str" xml:space="preserve">
+      <c r="G40" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H40" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to tournament creation page
 2. Verify title minimum length constraint (&lt; 3 characters)
 3. Verify chronological date constraint (start date after registration deadline)</v>
       </c>
-      <c r="I18" t="str">
+      <c r="I40" t="str">
         <v>Successfully completes execution: Verify chronological date constraint (start date after registration deadline) without errors.</v>
       </c>
-      <c r="J18" t="str">
+      <c r="J40" t="str">
         <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
       </c>
-      <c r="K18" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L18" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M18" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19" t="str">
+      <c r="K40" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L40" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M40" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
         <v>TRN-003</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B41" t="str">
         <v>Tournament Management</v>
       </c>
-      <c r="C19" t="str">
+      <c r="C41" t="str">
         <v>Tournament Management CRUD &amp; Validation Operations</v>
       </c>
-      <c r="D19" t="str">
+      <c r="D41" t="str">
         <v>READ: should navigate to tournament details and inspect overview, participants, and tabs</v>
       </c>
-      <c r="E19" t="str">
+      <c r="E41" t="str">
         <v>Executes READ: should navigate to tournament details and inspect overview, participants, and tabs. Grouped verification includes: Create tournament prerequisite, Search and navigate to tournament details page, Switch between tabs and verify content containers.</v>
       </c>
-      <c r="F19" t="str">
+      <c r="F41" t="str">
         <v>CRUD - Read (Positive)</v>
       </c>
-      <c r="G19" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H19" t="str" xml:space="preserve">
+      <c r="G41" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H41" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create tournament prerequisite
 2. Search and navigate to tournament details page
 3. Switch between tabs and verify content containers</v>
       </c>
-      <c r="I19" t="str">
+      <c r="I41" t="str">
         <v>Successfully completes execution: Switch between tabs and verify content containers without errors.</v>
       </c>
-      <c r="J19" t="str">
+      <c r="J41" t="str">
         <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
       </c>
-      <c r="K19" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L19" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M19" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="20" xml:space="preserve">
-      <c r="A20" t="str">
+      <c r="K41" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L41" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M41" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
         <v>TRN-004</v>
       </c>
-      <c r="B20" t="str">
+      <c r="B42" t="str">
         <v>Tournament Management</v>
       </c>
-      <c r="C20" t="str">
+      <c r="C42" t="str">
         <v>Tournament Management CRUD &amp; Validation Operations</v>
       </c>
-      <c r="D20" t="str">
+      <c r="D42" t="str">
         <v>UPDATE: should edit tournament details from settings tab and verify updates in real-time</v>
       </c>
-      <c r="E20" t="str">
+      <c r="E42" t="str">
         <v>Executes UPDATE: should edit tournament details from settings tab and verify updates in real-time. Grouped verification includes: Create tournament prerequisite, Navigate to tournament details page, Update tournament settings with new fields, Verify success alert and updated hero title in real-time.</v>
       </c>
-      <c r="F20" t="str">
+      <c r="F42" t="str">
         <v>CRUD - Update (Positive)</v>
       </c>
-      <c r="G20" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H20" t="str" xml:space="preserve">
+      <c r="G42" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H42" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create tournament prerequisite
 2. Navigate to tournament details page
 3. Update tournament settings with new fields
 4. Verify success alert and updated hero title in real-time</v>
       </c>
-      <c r="I20" t="str">
+      <c r="I42" t="str">
         <v>Successfully completes execution: Verify success alert and updated hero title in real-time without errors.</v>
       </c>
-      <c r="J20" t="str">
+      <c r="J42" t="str">
         <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
       </c>
-      <c r="K20" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L20" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M20" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21" t="str">
+      <c r="K42" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L42" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M42" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
         <v>TRN-005</v>
       </c>
-      <c r="B21" t="str">
+      <c r="B43" t="str">
         <v>Tournament Management</v>
       </c>
-      <c r="C21" t="str">
+      <c r="C43" t="str">
         <v>Tournament Management CRUD &amp; Validation Operations</v>
       </c>
-      <c r="D21" t="str">
+      <c r="D43" t="str">
         <v>STATUS &amp; REGISTRATION: should change operational status and allow player registration</v>
       </c>
-      <c r="E21" t="str">
+      <c r="E43" t="str">
         <v>Executes STATUS &amp; REGISTRATION: should change operational status and allow player registration. Grouped verification includes: Create tournament prerequisite, Navigate to tournament details page, Change status to ACTIVE via Settings tab, Register current authenticated user for tournament, Verify participant count incremented.</v>
       </c>
-      <c r="F21" t="str">
+      <c r="F43" t="str">
         <v>State Transition</v>
       </c>
-      <c r="G21" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H21" t="str" xml:space="preserve">
+      <c r="G43" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H43" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create tournament prerequisite
 2. Navigate to tournament details page
 3. Change status to ACTIVE via Settings tab
 4. Register current authenticated user for tournament
 5. Verify participant count incremented</v>
       </c>
-      <c r="I21" t="str">
+      <c r="I43" t="str">
         <v>Successfully completes execution: Verify participant count incremented without errors.</v>
       </c>
-      <c r="J21" t="str">
+      <c r="J43" t="str">
         <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
       </c>
-      <c r="K21" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L21" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M21" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="22" xml:space="preserve">
-      <c r="A22" t="str">
+      <c r="K43" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L43" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M43" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
         <v>TRN-006</v>
       </c>
-      <c r="B22" t="str">
+      <c r="B44" t="str">
         <v>Tournament Management</v>
       </c>
-      <c r="C22" t="str">
+      <c r="C44" t="str">
         <v>Tournament Management CRUD &amp; Validation Operations</v>
       </c>
-      <c r="D22" t="str">
+      <c r="D44" t="str">
         <v>DELETE: should soft-delete tournament and verify removal from directory</v>
       </c>
-      <c r="E22" t="str">
+      <c r="E44" t="str">
         <v>Executes DELETE: should soft-delete tournament and verify removal from directory. Grouped verification includes: Create tournament prerequisite, Navigate to tournament details page, Accept confirmation dialog and delete tournament from hero, Verify redirection and tournament removed from directory.</v>
       </c>
-      <c r="F22" t="str">
+      <c r="F44" t="str">
         <v>CRUD - Delete</v>
       </c>
-      <c r="G22" t="str">
+      <c r="G44" t="str">
         <v>P0 (Critical)</v>
       </c>
-      <c r="H22" t="str" xml:space="preserve">
+      <c r="H44" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create tournament prerequisite
 2. Navigate to tournament details page
 3. Accept confirmation dialog and delete tournament from hero
 4. Verify redirection and tournament removed from directory</v>
       </c>
-      <c r="I22" t="str">
+      <c r="I44" t="str">
         <v>Successfully completes execution: Verify redirection and tournament removed from directory without errors.</v>
       </c>
-      <c r="J22" t="str">
+      <c r="J44" t="str">
         <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
       </c>
-      <c r="K22" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L22" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M22" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="23" xml:space="preserve">
-      <c r="A23" t="str">
+      <c r="K44" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L44" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M44" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
         <v>USER-001</v>
       </c>
-      <c r="B23" t="str">
+      <c r="B45" t="str">
         <v>Member Management</v>
       </c>
-      <c r="C23" t="str">
+      <c r="C45" t="str">
         <v>User &amp; Member Management CRUD Operations</v>
       </c>
-      <c r="D23" t="str">
+      <c r="D45" t="str">
         <v>CREATE: should create a new user/member successfully and display in directory</v>
       </c>
-      <c r="E23" t="str">
+      <c r="E45" t="str">
         <v>Executes CREATE: should create a new user/member successfully and display in directory. Grouped verification includes: Navigate to member management directory, Open user creation form, Fill and submit user creation form with DataFactory payload, Verify redirection back to member directory, Search for the newly created user and verify presence in table.</v>
       </c>
-      <c r="F23" t="str">
+      <c r="F45" t="str">
         <v>CRUD - Create (Positive)</v>
       </c>
-      <c r="G23" t="str">
+      <c r="G45" t="str">
         <v>P0 (Critical)</v>
       </c>
-      <c r="H23" t="str" xml:space="preserve">
+      <c r="H45" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to member management directory
 2. Open user creation form
 3. Fill and submit user creation form with DataFactory payload
 4. Verify redirection back to member directory
 5. Search for the newly created user and verify presence in table</v>
       </c>
-      <c r="I23" t="str">
+      <c r="I45" t="str">
         <v>Successfully completes execution: Search for the newly created user and verify presence in table without errors.</v>
       </c>
-      <c r="J23" t="str">
+      <c r="J45" t="str">
         <v>apps/tt-client/tests/user-crud.spec.ts</v>
       </c>
-      <c r="K23" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L23" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M23" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="24" xml:space="preserve">
-      <c r="A24" t="str">
+      <c r="K45" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L45" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M45" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
         <v>USER-002</v>
       </c>
-      <c r="B24" t="str">
+      <c r="B46" t="str">
         <v>Member Management</v>
       </c>
-      <c r="C24" t="str">
+      <c r="C46" t="str">
         <v>User &amp; Member Management CRUD Operations</v>
       </c>
-      <c r="D24" t="str">
+      <c r="D46" t="str">
         <v>READ: should navigate to user profile and view complete details</v>
       </c>
-      <c r="E24" t="str">
+      <c r="E46" t="str">
         <v>Executes READ: should navigate to user profile and view complete details. Grouped verification includes: Create user for profile inspection, Filter/search to locate the created user, Click user name link to navigate to details page, Verify member details page renders with matching identity.</v>
       </c>
-      <c r="F24" t="str">
+      <c r="F46" t="str">
         <v>CRUD - Read (Positive)</v>
       </c>
-      <c r="G24" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H24" t="str" xml:space="preserve">
+      <c r="G46" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H46" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create user for profile inspection
 2. Filter/search to locate the created user
 3. Click user name link to navigate to details page
 4. Verify member details page renders with matching identity</v>
       </c>
-      <c r="I24" t="str">
+      <c r="I46" t="str">
         <v>Successfully completes execution: Verify member details page renders with matching identity without errors.</v>
       </c>
-      <c r="J24" t="str">
+      <c r="J46" t="str">
         <v>apps/tt-client/tests/user-crud.spec.ts</v>
       </c>
-      <c r="K24" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L24" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M24" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="25" xml:space="preserve">
-      <c r="A25" t="str">
+      <c r="K46" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L46" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M46" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
         <v>USER-003</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B47" t="str">
         <v>Member Management</v>
       </c>
-      <c r="C25" t="str">
+      <c r="C47" t="str">
         <v>User &amp; Member Management CRUD Operations</v>
       </c>
-      <c r="D25" t="str">
+      <c r="D47" t="str">
         <v>UPDATE: should update user details (name, role, status) and verify changes</v>
       </c>
-      <c r="E25" t="str">
+      <c r="E47" t="str">
         <v>Executes UPDATE: should update user details (name, role, status) and verify changes. Grouped verification includes: Create target user for updating, Locate user and open edit page via action dropdown, Apply updates to user details, Verify redirection to profile and updated details.</v>
       </c>
-      <c r="F25" t="str">
+      <c r="F47" t="str">
         <v>CRUD - Update (Positive)</v>
       </c>
-      <c r="G25" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H25" t="str" xml:space="preserve">
+      <c r="G47" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H47" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create target user for updating
 2. Locate user and open edit page via action dropdown
 3. Apply updates to user details
 4. Verify redirection to profile and updated details</v>
       </c>
-      <c r="I25" t="str">
+      <c r="I47" t="str">
         <v>Successfully completes execution: Verify redirection to profile and updated details without errors.</v>
       </c>
-      <c r="J25" t="str">
+      <c r="J47" t="str">
         <v>apps/tt-client/tests/user-crud.spec.ts</v>
       </c>
-      <c r="K25" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L25" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M25" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="26" xml:space="preserve">
-      <c r="A26" t="str">
+      <c r="K47" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L47" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M47" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
         <v>USER-004</v>
       </c>
-      <c r="B26" t="str">
+      <c r="B48" t="str">
         <v>Member Management</v>
       </c>
-      <c r="C26" t="str">
+      <c r="C48" t="str">
         <v>User &amp; Member Management CRUD Operations</v>
       </c>
-      <c r="D26" t="str">
+      <c r="D48" t="str">
         <v>STATUS TOGGLE: should toggle user account status between active and inactive</v>
       </c>
-      <c r="E26" t="str">
+      <c r="E48" t="str">
         <v>Executes STATUS TOGGLE: should toggle user account status between active and inactive. Grouped verification includes: Create user for status toggling, Search for the member in directory, Open dropdown menu and toggle account status, Verify status badge updates to Inactive.</v>
       </c>
-      <c r="F26" t="str">
+      <c r="F48" t="str">
         <v>State Transition</v>
       </c>
-      <c r="G26" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H26" t="str" xml:space="preserve">
+      <c r="G48" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H48" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create user for status toggling
 2. Search for the member in directory
 3. Open dropdown menu and toggle account status
 4. Verify status badge updates to Inactive</v>
       </c>
-      <c r="I26" t="str">
+      <c r="I48" t="str">
         <v>Successfully completes execution: Verify status badge updates to Inactive without errors.</v>
       </c>
-      <c r="J26" t="str">
+      <c r="J48" t="str">
         <v>apps/tt-client/tests/user-crud.spec.ts</v>
       </c>
-      <c r="K26" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L26" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M26" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="27" xml:space="preserve">
-      <c r="A27" t="str">
+      <c r="K48" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L48" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M48" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str">
         <v>USER-005</v>
       </c>
-      <c r="B27" t="str">
+      <c r="B49" t="str">
         <v>Member Management</v>
       </c>
-      <c r="C27" t="str">
+      <c r="C49" t="str">
         <v>User &amp; Member Management CRUD Operations</v>
       </c>
-      <c r="D27" t="str">
+      <c r="D49" t="str">
         <v>DELETE: should soft-delete user and verify removal from directory</v>
       </c>
-      <c r="E27" t="str">
+      <c r="E49" t="str">
         <v>Executes DELETE: should soft-delete user and verify removal from directory. Grouped verification includes: Create user to delete, Search and locate member in directory, Navigate to details page and trigger deletion with confirmation dialog, Verify redirected to /members and user is no longer listed.</v>
       </c>
-      <c r="F27" t="str">
+      <c r="F49" t="str">
         <v>CRUD - Delete</v>
       </c>
-      <c r="G27" t="str">
+      <c r="G49" t="str">
         <v>P0 (Critical)</v>
       </c>
-      <c r="H27" t="str" xml:space="preserve">
+      <c r="H49" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create user to delete
 2. Search and locate member in directory
 3. Navigate to details page and trigger deletion with confirmation dialog
 4. Verify redirected to /members and user is no longer listed</v>
       </c>
-      <c r="I27" t="str">
+      <c r="I49" t="str">
         <v>Successfully completes execution: Verify redirected to /members and user is no longer listed without errors.</v>
       </c>
-      <c r="J27" t="str">
+      <c r="J49" t="str">
         <v>apps/tt-client/tests/user-crud.spec.ts</v>
       </c>
-      <c r="K27" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L27" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M27" t="str">
+      <c r="K49" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L49" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M49" t="str">
         <v>2026-10-13</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M49"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2263,6 +5014,162 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="45.83203125" customWidth="1"/>
+    <col min="5" max="5" width="55.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
+    <col min="9" max="9" width="45.83203125" customWidth="1"/>
+    <col min="10" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Module</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Scenario Group</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Test Type</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Automated Steps</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Expected Result</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Spec File</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Created At</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Last Updated</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>HOME-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Home Landing Portal</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Home Landing Page &amp; Public Information Portal</v>
+      </c>
+      <c r="D2" t="str">
+        <v>HOME-01: Public Landing Access - Unauthenticated guest can view Home page with hero, live stats, and sport categories</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Executes HOME-01: Public Landing Access - Unauthenticated guest can view Home page with hero, live stats, and sport categories. Grouped verification includes: Navigate to root path as guest and verify no redirect to login, Verify Topbar renders guest navigation controls, Verify Home Hero banner and live sports platform headline, Verify multi-sport categories showcase contains all supported sports, Click sport category filter and verify active button state.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G2" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to root path as guest and verify no redirect to login
+2. Verify Topbar renders guest navigation controls
+3. Verify Home Hero banner and live sports platform headline
+4. Verify multi-sport categories showcase contains all supported sports
+5. Click sport category filter and verify active button state</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Successfully completes execution: Click sport category filter and verify active button state without errors.</v>
+      </c>
+      <c r="J2" t="str">
+        <v>apps/tt-client/tests/home.spec.ts</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>HOME-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Home Landing Portal</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Home Landing Page &amp; Public Information Portal</v>
+      </c>
+      <c r="D3" t="str">
+        <v>HOME-02: Authenticated Experience - Seamless transition with personalized topbar and sidebar navigation</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Executes HOME-02: Authenticated Experience - Seamless transition with personalized topbar and sidebar navigation. Grouped verification includes: Authenticate seeded player session, Navigate to Home via Sidebar navigation, Verify authenticated Topbar displays user greeting and sign out action, Verify Featured Latest Tournament and Current Match cards exist.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>State Transition</v>
+      </c>
+      <c r="G3" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Authenticate seeded player session
+2. Navigate to Home via Sidebar navigation
+3. Verify authenticated Topbar displays user greeting and sign out action
+4. Verify Featured Latest Tournament and Current Match cards exist</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Successfully completes execution: Verify Featured Latest Tournament and Current Match cards exist without errors.</v>
+      </c>
+      <c r="J3" t="str">
+        <v>apps/tt-client/tests/home.spec.ts</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
@@ -2376,9 +5283,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -2438,19 +5345,19 @@
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>SPRT-001</v>
+        <v>BDMT-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Multi-Sport Tournaments</v>
+        <v>Badminton Matches</v>
       </c>
       <c r="C2" t="str">
-        <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
+        <v>Badminton Matches &amp; Sets Progression</v>
       </c>
       <c r="D2" t="str">
-        <v>SPRT-01: Multi-Sport Form Adapters - sport presets auto-populate format, team limits, and rules</v>
+        <v>BDMT-01: Badminton Tournament Setup - Best of 3 sets to 21 points preset</v>
       </c>
       <c r="E2" t="str">
-        <v>Executes SPRT-01: Multi-Sport Form Adapters - sport presets auto-populate format, team limits, and rules. Grouped verification includes: Navigate to Create Tournament page, Verify default Table Tennis preset configuration, Select Cricket sport card and verify adaptive fields for team competition, Select Chess sport card and verify scoring format is GAME_POINTS, Test quick rule template chip appending and live preview tab.</v>
+        <v>Executes BDMT-01: Badminton Tournament Setup - Best of 3 sets to 21 points preset. Grouped verification includes: Select Badminton sport card and verify 21-points set scoring configuration, Fill form details and submit Badminton tournament, Verify Badminton card appears on Tournaments listing.</v>
       </c>
       <c r="F2" t="str">
         <v>Functional E2E</v>
@@ -2459,17 +5366,15 @@
         <v>P1 (High)</v>
       </c>
       <c r="H2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to Create Tournament page
-2. Verify default Table Tennis preset configuration
-3. Select Cricket sport card and verify adaptive fields for team competition
-4. Select Chess sport card and verify scoring format is GAME_POINTS
-5. Test quick rule template chip appending and live preview tab</v>
+        <v xml:space="preserve">1. Select Badminton sport card and verify 21-points set scoring configuration
+2. Fill form details and submit Badminton tournament
+3. Verify Badminton card appears on Tournaments listing</v>
       </c>
       <c r="I2" t="str">
-        <v>Successfully completes execution: Test quick rule template chip appending and live preview tab without errors.</v>
+        <v>Successfully completes execution: Verify Badminton card appears on Tournaments listing without errors.</v>
       </c>
       <c r="J2" t="str">
-        <v>apps/tt-client/tests/multi-sport.spec.ts</v>
+        <v>apps/tt-client/tests/matches/badminton.spec.ts</v>
       </c>
       <c r="K2" t="str">
         <v>Automated &amp; Passing</v>
@@ -2483,37 +5388,38 @@
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>SPRT-002</v>
+        <v>BDMT-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Multi-Sport Tournaments</v>
+        <v>Badminton Matches</v>
       </c>
       <c r="C3" t="str">
-        <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
+        <v>Badminton Matches &amp; Sets Progression</v>
       </c>
       <c r="D3" t="str">
-        <v>SPRT-02: Duplicate Registration Guard - prevents re-registration and displays Already Registered badge</v>
+        <v>BDMT-02: Badminton Match Play - Bracket match draw, set score entry, and finals champion</v>
       </c>
       <c r="E3" t="str">
-        <v>Executes SPRT-02: Duplicate Registration Guard - prevents re-registration and displays Already Registered badge. Grouped verification includes: Create an individual tournament, Open tournament and register current user, Verify Hero now shows Already Registered badge and register button is removed, Verify user is listed in Participants tab.</v>
+        <v>Executes BDMT-02: Badminton Match Play - Bracket match draw, set score entry, and finals champion. Grouped verification includes: Create Badminton tournament and open details, Seed 4 badminton players and generate opening knockout matches, Record 21-points set score for Semifinal Match 1 (21 - 17), Record 21-points set score for Semifinal Match 2 (18 - 21), Record Grand Final score (21 - 19) and verify championship crown.</v>
       </c>
       <c r="F3" t="str">
-        <v>UI / Functional</v>
+        <v>Functional E2E</v>
       </c>
       <c r="G3" t="str">
-        <v>P0 (Critical)</v>
+        <v>P1 (High)</v>
       </c>
       <c r="H3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Create an individual tournament
-2. Open tournament and register current user
-3. Verify Hero now shows Already Registered badge and register button is removed
-4. Verify user is listed in Participants tab</v>
+        <v xml:space="preserve">1. Create Badminton tournament and open details
+2. Seed 4 badminton players and generate opening knockout matches
+3. Record 21-points set score for Semifinal Match 1 (21 - 17)
+4. Record 21-points set score for Semifinal Match 2 (18 - 21)
+5. Record Grand Final score (21 - 19) and verify championship crown</v>
       </c>
       <c r="I3" t="str">
-        <v>Successfully completes execution: Verify user is listed in Participants tab without errors.</v>
+        <v>Successfully completes execution: Record Grand Final score (21 - 19) and verify championship crown without errors.</v>
       </c>
       <c r="J3" t="str">
-        <v>apps/tt-client/tests/multi-sport.spec.ts</v>
+        <v>apps/tt-client/tests/matches/badminton.spec.ts</v>
       </c>
       <c r="K3" t="str">
         <v>Automated &amp; Passing</v>
@@ -2522,108 +5428,19 @@
         <v>2026-10-13</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4" t="str">
-        <v>SPRT-003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Multi-Sport Tournaments</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
-      </c>
-      <c r="D4" t="str">
-        <v>SPRT-03: Team Sports Registration - team modal, min team size enforcement, and unique player assignment</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Executes SPRT-03: Team Sports Registration - team modal, min team size enforcement, and unique player assignment. Grouped verification includes: Create a team Cricket tournament with minTeamSize = 2, Open Cricket tournament details and click Register Team, Verify Register Team Modal opens and enforces minimum team size, Add additional member and successfully submit team.</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Functional E2E</v>
-      </c>
-      <c r="G4" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Create a team Cricket tournament with minTeamSize = 2
-2. Open Cricket tournament details and click Register Team
-3. Verify Register Team Modal opens and enforces minimum team size
-4. Add additional member and successfully submit team</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Successfully completes execution: Add additional member and successfully submit team without errors.</v>
-      </c>
-      <c r="J4" t="str">
-        <v>apps/tt-client/tests/multi-sport.spec.ts</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L4" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M4" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5" t="str">
-        <v>SPRT-004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Multi-Sport Tournaments</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
-      </c>
-      <c r="D5" t="str">
-        <v>SPRT-04: Wave-by-Wave Progression &amp; Sport Scoring - registration lock, wave draws, sport-specific score entry, and finals crowning</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Executes SPRT-04: Wave-by-Wave Progression &amp; Sport Scoring - registration lock, wave draws, sport-specific score entry, and finals crowning. Grouped verification includes: Create tournament and navigate to matches tab, Verify registration window status is initially open, Seed 4 dummy players to populate participants, Verify matches tab renders bracket round 1 with sport-specific scoring modal triggers, Complete remaining matches and verify Grand Final champion banner.</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Functional E2E</v>
-      </c>
-      <c r="G5" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Create tournament and navigate to matches tab
-2. Verify registration window status is initially open
-3. Seed 4 dummy players to populate participants
-4. Verify matches tab renders bracket round 1 with sport-specific scoring modal triggers
-5. Complete remaining matches and verify Grand Final champion banner</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Successfully completes execution: Complete remaining matches and verify Grand Final champion banner without errors.</v>
-      </c>
-      <c r="J5" t="str">
-        <v>apps/tt-client/tests/multi-sport.spec.ts</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L5" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M5" t="str">
         <v>2026-10-13</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -2683,38 +5500,36 @@
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>TRN-001</v>
+        <v>CRRM-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Tournament Management</v>
+        <v>Carrom Matches</v>
       </c>
       <c r="C2" t="str">
-        <v>Tournament Management CRUD &amp; Validation Operations</v>
+        <v>Carrom Board Matches &amp; Points Progression</v>
       </c>
       <c r="D2" t="str">
-        <v>CREATE: should create a new tournament successfully with valid data and show in directory</v>
+        <v>CRRM-01: Carrom Board Tournament Setup - Auto-populates 25 points rule preset</v>
       </c>
       <c r="E2" t="str">
-        <v>Executes CREATE: should create a new tournament successfully with valid data and show in directory. Grouped verification includes: Navigate to tournaments list, Open tournament creation form, Fill and submit tournament form with valid payload, Verify redirection back to tournaments directory, Search for created tournament and verify presence in grid.</v>
+        <v>Executes CRRM-01: Carrom Board Tournament Setup - Auto-populates 25 points rule preset. Grouped verification includes: Select Carrom sport preset and verify rules and points configuration, Submit Carrom tournament form, Verify tournament card in directory.</v>
       </c>
       <c r="F2" t="str">
-        <v>CRUD - Create (Positive)</v>
+        <v>Functional E2E</v>
       </c>
       <c r="G2" t="str">
-        <v>P0 (Critical)</v>
+        <v>P1 (High)</v>
       </c>
       <c r="H2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to tournaments list
-2. Open tournament creation form
-3. Fill and submit tournament form with valid payload
-4. Verify redirection back to tournaments directory
-5. Search for created tournament and verify presence in grid</v>
+        <v xml:space="preserve">1. Select Carrom sport preset and verify rules and points configuration
+2. Submit Carrom tournament form
+3. Verify tournament card in directory</v>
       </c>
       <c r="I2" t="str">
-        <v>Successfully completes execution: Search for created tournament and verify presence in grid without errors.</v>
+        <v>Successfully completes execution: Verify tournament card in directory without errors.</v>
       </c>
       <c r="J2" t="str">
-        <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
+        <v>apps/tt-client/tests/matches/carrom.spec.ts</v>
       </c>
       <c r="K2" t="str">
         <v>Automated &amp; Passing</v>
@@ -2728,36 +5543,38 @@
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>TRN-002</v>
+        <v>CRRM-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Tournament Management</v>
+        <v>Carrom Matches</v>
       </c>
       <c r="C3" t="str">
-        <v>Tournament Management CRUD &amp; Validation Operations</v>
+        <v>Carrom Board Matches &amp; Points Progression</v>
       </c>
       <c r="D3" t="str">
-        <v>VALIDATION: should enforce client-side date &amp; length constraints on tournament creation</v>
+        <v>CRRM-02: Carrom Match Fixtures &amp; Point Scoring to 25 with Queen bonus</v>
       </c>
       <c r="E3" t="str">
-        <v>Executes VALIDATION: should enforce client-side date &amp; length constraints on tournament creation. Grouped verification includes: Navigate to tournament creation page, Verify title minimum length constraint (&lt; 3 characters), Verify chronological date constraint (start date after registration deadline).</v>
+        <v>Executes CRRM-02: Carrom Match Fixtures &amp; Point Scoring to 25 with Queen bonus. Grouped verification includes: Create Carrom tournament and open details, Seed 4 carrom players and generate Round 1 board fixtures, Submit board points (25 - 18) for first semifinal board match, Submit board points for second match and advance to Grand Final, Submit final board score (25 - 21) and crown Carrom Champion.</v>
       </c>
       <c r="F3" t="str">
-        <v>Validation (Negative)</v>
+        <v>Functional E2E</v>
       </c>
       <c r="G3" t="str">
         <v>P1 (High)</v>
       </c>
       <c r="H3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to tournament creation page
-2. Verify title minimum length constraint (&lt; 3 characters)
-3. Verify chronological date constraint (start date after registration deadline)</v>
+        <v xml:space="preserve">1. Create Carrom tournament and open details
+2. Seed 4 carrom players and generate Round 1 board fixtures
+3. Submit board points (25 - 18) for first semifinal board match
+4. Submit board points for second match and advance to Grand Final
+5. Submit final board score (25 - 21) and crown Carrom Champion</v>
       </c>
       <c r="I3" t="str">
-        <v>Successfully completes execution: Verify chronological date constraint (start date after registration deadline) without errors.</v>
+        <v>Successfully completes execution: Submit final board score (25 - 21) and crown Carrom Champion without errors.</v>
       </c>
       <c r="J3" t="str">
-        <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
+        <v>apps/tt-client/tests/matches/carrom.spec.ts</v>
       </c>
       <c r="K3" t="str">
         <v>Automated &amp; Passing</v>
@@ -2766,195 +5583,19 @@
         <v>2026-10-13</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4" t="str">
-        <v>TRN-003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Tournament Management</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Tournament Management CRUD &amp; Validation Operations</v>
-      </c>
-      <c r="D4" t="str">
-        <v>READ: should navigate to tournament details and inspect overview, participants, and tabs</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Executes READ: should navigate to tournament details and inspect overview, participants, and tabs. Grouped verification includes: Create tournament prerequisite, Search and navigate to tournament details page, Switch between tabs and verify content containers.</v>
-      </c>
-      <c r="F4" t="str">
-        <v>CRUD - Read (Positive)</v>
-      </c>
-      <c r="G4" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Create tournament prerequisite
-2. Search and navigate to tournament details page
-3. Switch between tabs and verify content containers</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Successfully completes execution: Switch between tabs and verify content containers without errors.</v>
-      </c>
-      <c r="J4" t="str">
-        <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L4" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M4" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5" t="str">
-        <v>TRN-004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Tournament Management</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Tournament Management CRUD &amp; Validation Operations</v>
-      </c>
-      <c r="D5" t="str">
-        <v>UPDATE: should edit tournament details from settings tab and verify updates in real-time</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Executes UPDATE: should edit tournament details from settings tab and verify updates in real-time. Grouped verification includes: Create tournament prerequisite, Navigate to tournament details page, Update tournament settings with new fields, Verify success alert and updated hero title in real-time.</v>
-      </c>
-      <c r="F5" t="str">
-        <v>CRUD - Update (Positive)</v>
-      </c>
-      <c r="G5" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Create tournament prerequisite
-2. Navigate to tournament details page
-3. Update tournament settings with new fields
-4. Verify success alert and updated hero title in real-time</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Successfully completes execution: Verify success alert and updated hero title in real-time without errors.</v>
-      </c>
-      <c r="J5" t="str">
-        <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L5" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M5" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6" t="str">
-        <v>TRN-005</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Tournament Management</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Tournament Management CRUD &amp; Validation Operations</v>
-      </c>
-      <c r="D6" t="str">
-        <v>STATUS &amp; REGISTRATION: should change operational status and allow player registration</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Executes STATUS &amp; REGISTRATION: should change operational status and allow player registration. Grouped verification includes: Create tournament prerequisite, Navigate to tournament details page, Change status to ACTIVE via Settings tab, Register current authenticated user for tournament, Verify participant count incremented.</v>
-      </c>
-      <c r="F6" t="str">
-        <v>State Transition</v>
-      </c>
-      <c r="G6" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H6" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Create tournament prerequisite
-2. Navigate to tournament details page
-3. Change status to ACTIVE via Settings tab
-4. Register current authenticated user for tournament
-5. Verify participant count incremented</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Successfully completes execution: Verify participant count incremented without errors.</v>
-      </c>
-      <c r="J6" t="str">
-        <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
-      </c>
-      <c r="K6" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L6" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M6" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7" t="str">
-        <v>TRN-006</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Tournament Management</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Tournament Management CRUD &amp; Validation Operations</v>
-      </c>
-      <c r="D7" t="str">
-        <v>DELETE: should soft-delete tournament and verify removal from directory</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Executes DELETE: should soft-delete tournament and verify removal from directory. Grouped verification includes: Create tournament prerequisite, Navigate to tournament details page, Accept confirmation dialog and delete tournament from hero, Verify redirection and tournament removed from directory.</v>
-      </c>
-      <c r="F7" t="str">
-        <v>CRUD - Delete</v>
-      </c>
-      <c r="G7" t="str">
-        <v>P0 (Critical)</v>
-      </c>
-      <c r="H7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Create tournament prerequisite
-2. Navigate to tournament details page
-3. Accept confirmation dialog and delete tournament from hero
-4. Verify redirection and tournament removed from directory</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Successfully completes execution: Verify redirection and tournament removed from directory without errors.</v>
-      </c>
-      <c r="J7" t="str">
-        <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L7" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M7" t="str">
         <v>2026-10-13</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -3014,38 +5655,36 @@
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>USER-001</v>
+        <v>CHSS-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Member Management</v>
+        <v>Chess Matches</v>
       </c>
       <c r="C2" t="str">
-        <v>User &amp; Member Management CRUD Operations</v>
+        <v>Chess Duels &amp; FIDE Points Progression</v>
       </c>
       <c r="D2" t="str">
-        <v>CREATE: should create a new user/member successfully and display in directory</v>
+        <v>CHSS-01: Chess Rapid Tournament Setup - Enforces Individual mode and GAME_POINTS scoring</v>
       </c>
       <c r="E2" t="str">
-        <v>Executes CREATE: should create a new user/member successfully and display in directory. Grouped verification includes: Navigate to member management directory, Open user creation form, Fill and submit user creation form with DataFactory payload, Verify redirection back to member directory, Search for the newly created user and verify presence in table.</v>
+        <v>Executes CHSS-01: Chess Rapid Tournament Setup - Enforces Individual mode and GAME_POINTS scoring. Grouped verification includes: Select Chess sport card and verify individual duel mode, Submit Chess tournament form, Verify Chess tournament appears in tournament directory.</v>
       </c>
       <c r="F2" t="str">
-        <v>CRUD - Create (Positive)</v>
+        <v>Functional E2E</v>
       </c>
       <c r="G2" t="str">
-        <v>P0 (Critical)</v>
+        <v>P1 (High)</v>
       </c>
       <c r="H2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to member management directory
-2. Open user creation form
-3. Fill and submit user creation form with DataFactory payload
-4. Verify redirection back to member directory
-5. Search for the newly created user and verify presence in table</v>
+        <v xml:space="preserve">1. Select Chess sport card and verify individual duel mode
+2. Submit Chess tournament form
+3. Verify Chess tournament appears in tournament directory</v>
       </c>
       <c r="I2" t="str">
-        <v>Successfully completes execution: Search for the newly created user and verify presence in table without errors.</v>
+        <v>Successfully completes execution: Verify Chess tournament appears in tournament directory without errors.</v>
       </c>
       <c r="J2" t="str">
-        <v>apps/tt-client/tests/user-crud.spec.ts</v>
+        <v>apps/tt-client/tests/matches/chess.spec.ts</v>
       </c>
       <c r="K2" t="str">
         <v>Automated &amp; Passing</v>
@@ -3059,37 +5698,192 @@
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>USER-002</v>
+        <v>CHSS-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Member Management</v>
+        <v>Chess Matches</v>
       </c>
       <c r="C3" t="str">
-        <v>User &amp; Member Management CRUD Operations</v>
+        <v>Chess Duels &amp; FIDE Points Progression</v>
       </c>
       <c r="D3" t="str">
-        <v>READ: should navigate to user profile and view complete details</v>
+        <v>CHSS-02: Chess Duel Progression - Match draw, 1.0 vs 0.0 scoring, and championship crowning</v>
       </c>
       <c r="E3" t="str">
-        <v>Executes READ: should navigate to user profile and view complete details. Grouped verification includes: Create user for profile inspection, Filter/search to locate the created user, Click user name link to navigate to details page, Verify member details page renders with matching identity.</v>
+        <v>Executes CHSS-02: Chess Duel Progression - Match draw, 1.0 vs 0.0 scoring, and championship crowning. Grouped verification includes: Create Chess tournament and open details, Seed 4 chess players and generate opening duel fixtures, Submit game point results for semifinal duels (1 - 0), Submit Grand Final game result and crown Chess Champion.</v>
       </c>
       <c r="F3" t="str">
-        <v>CRUD - Read (Positive)</v>
+        <v>Functional E2E</v>
       </c>
       <c r="G3" t="str">
         <v>P1 (High)</v>
       </c>
       <c r="H3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Create user for profile inspection
-2. Filter/search to locate the created user
-3. Click user name link to navigate to details page
-4. Verify member details page renders with matching identity</v>
+        <v xml:space="preserve">1. Create Chess tournament and open details
+2. Seed 4 chess players and generate opening duel fixtures
+3. Submit game point results for semifinal duels (1 - 0)
+4. Submit Grand Final game result and crown Chess Champion</v>
       </c>
       <c r="I3" t="str">
-        <v>Successfully completes execution: Verify member details page renders with matching identity without errors.</v>
+        <v>Successfully completes execution: Submit Grand Final game result and crown Chess Champion without errors.</v>
       </c>
       <c r="J3" t="str">
-        <v>apps/tt-client/tests/user-crud.spec.ts</v>
+        <v>apps/tt-client/tests/matches/chess.spec.ts</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M4"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="45.83203125" customWidth="1"/>
+    <col min="5" max="5" width="55.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
+    <col min="9" max="9" width="45.83203125" customWidth="1"/>
+    <col min="10" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Module</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Scenario Group</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Test Type</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Automated Steps</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Expected Result</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Spec File</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Created At</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Last Updated</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>CRKT-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Cricket Matches</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Cricket Matches &amp; Squad Progression</v>
+      </c>
+      <c r="D2" t="str">
+        <v>CRKT-01: Cricket Squad Tournament Creation - Validates squad requirements and limited overs format</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Executes CRKT-01: Cricket Squad Tournament Creation - Validates squad requirements and limited overs format. Grouped verification includes: Navigate to Create Tournament page and select Cricket sport card, Verify team mode and squad limits adapt automatically, Fill schedule details and submit Cricket tournament, Verify Cricket tournament card appears on Tournaments list.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G2" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Create Tournament page and select Cricket sport card
+2. Verify team mode and squad limits adapt automatically
+3. Fill schedule details and submit Cricket tournament
+4. Verify Cricket tournament card appears on Tournaments list</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Successfully completes execution: Verify Cricket tournament card appears on Tournaments list without errors.</v>
+      </c>
+      <c r="J2" t="str">
+        <v>apps/tt-client/tests/matches/cricket.spec.ts</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>CRKT-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Cricket Matches</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Cricket Matches &amp; Squad Progression</v>
+      </c>
+      <c r="D3" t="str">
+        <v>CRKT-02: Cricket Team Registration &amp; Captain Nomination</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Executes CRKT-02: Cricket Team Registration &amp; Captain Nomination. Grouped verification includes: Create Cricket squad tournament with min team size 2, Open Cricket tournament details page, Trigger Team Registration modal and register Team Titan, Inspect registered teams list on Participants tab.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G3" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Create Cricket squad tournament with min team size 2
+2. Open Cricket tournament details page
+3. Trigger Team Registration modal and register Team Titan
+4. Inspect registered teams list on Participants tab</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Successfully completes execution: Inspect registered teams list on Participants tab without errors.</v>
+      </c>
+      <c r="J3" t="str">
+        <v>apps/tt-client/tests/matches/cricket.spec.ts</v>
       </c>
       <c r="K3" t="str">
         <v>Automated &amp; Passing</v>
@@ -3103,37 +5897,35 @@
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>USER-003</v>
+        <v>CRKT-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Member Management</v>
+        <v>Cricket Matches</v>
       </c>
       <c r="C4" t="str">
-        <v>User &amp; Member Management CRUD Operations</v>
+        <v>Cricket Matches &amp; Squad Progression</v>
       </c>
       <c r="D4" t="str">
-        <v>UPDATE: should update user details (name, role, status) and verify changes</v>
+        <v>CRKT-03: Cricket Wave 1 Fixtures &amp; Limited Overs Scoring</v>
       </c>
       <c r="E4" t="str">
-        <v>Executes UPDATE: should update user details (name, role, status) and verify changes. Grouped verification includes: Create target user for updating, Locate user and open edit page via action dropdown, Apply updates to user details, Verify redirection to profile and updated details.</v>
+        <v>Executes CRKT-03: Cricket Wave 1 Fixtures &amp; Limited Overs Scoring. Grouped verification includes: Create Cricket tournament and seed squad teams, Verify Wave 1 cricket fixture and submit limited overs run score.</v>
       </c>
       <c r="F4" t="str">
-        <v>CRUD - Update (Positive)</v>
+        <v>Functional E2E</v>
       </c>
       <c r="G4" t="str">
         <v>P1 (High)</v>
       </c>
       <c r="H4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Create target user for updating
-2. Locate user and open edit page via action dropdown
-3. Apply updates to user details
-4. Verify redirection to profile and updated details</v>
+        <v xml:space="preserve">1. Create Cricket tournament and seed squad teams
+2. Verify Wave 1 cricket fixture and submit limited overs run score</v>
       </c>
       <c r="I4" t="str">
-        <v>Successfully completes execution: Verify redirection to profile and updated details without errors.</v>
+        <v>Successfully completes execution: Verify Wave 1 cricket fixture and submit limited overs run score without errors.</v>
       </c>
       <c r="J4" t="str">
-        <v>apps/tt-client/tests/user-crud.spec.ts</v>
+        <v>apps/tt-client/tests/matches/cricket.spec.ts</v>
       </c>
       <c r="K4" t="str">
         <v>Automated &amp; Passing</v>
@@ -3142,100 +5934,12 @@
         <v>2026-10-13</v>
       </c>
       <c r="M4" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5" t="str">
-        <v>USER-004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Member Management</v>
-      </c>
-      <c r="C5" t="str">
-        <v>User &amp; Member Management CRUD Operations</v>
-      </c>
-      <c r="D5" t="str">
-        <v>STATUS TOGGLE: should toggle user account status between active and inactive</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Executes STATUS TOGGLE: should toggle user account status between active and inactive. Grouped verification includes: Create user for status toggling, Search for the member in directory, Open dropdown menu and toggle account status, Verify status badge updates to Inactive.</v>
-      </c>
-      <c r="F5" t="str">
-        <v>State Transition</v>
-      </c>
-      <c r="G5" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Create user for status toggling
-2. Search for the member in directory
-3. Open dropdown menu and toggle account status
-4. Verify status badge updates to Inactive</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Successfully completes execution: Verify status badge updates to Inactive without errors.</v>
-      </c>
-      <c r="J5" t="str">
-        <v>apps/tt-client/tests/user-crud.spec.ts</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L5" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M5" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6" t="str">
-        <v>USER-005</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Member Management</v>
-      </c>
-      <c r="C6" t="str">
-        <v>User &amp; Member Management CRUD Operations</v>
-      </c>
-      <c r="D6" t="str">
-        <v>DELETE: should soft-delete user and verify removal from directory</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Executes DELETE: should soft-delete user and verify removal from directory. Grouped verification includes: Create user to delete, Search and locate member in directory, Navigate to details page and trigger deletion with confirmation dialog, Verify redirected to /members and user is no longer listed.</v>
-      </c>
-      <c r="F6" t="str">
-        <v>CRUD - Delete</v>
-      </c>
-      <c r="G6" t="str">
-        <v>P0 (Critical)</v>
-      </c>
-      <c r="H6" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Create user to delete
-2. Search and locate member in directory
-3. Navigate to details page and trigger deletion with confirmation dialog
-4. Verify redirected to /members and user is no longer listed</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Successfully completes execution: Verify redirected to /members and user is no longer listed without errors.</v>
-      </c>
-      <c r="J6" t="str">
-        <v>apps/tt-client/tests/user-crud.spec.ts</v>
-      </c>
-      <c r="K6" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L6" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M6" t="str">
         <v>2026-10-13</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/test-artifact/web-tests.xlsx
+++ b/test-artifact/web-tests.xlsx
@@ -480,7 +480,7 @@
         <v>Total Automated Scenarios</v>
       </c>
       <c r="B8">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -488,7 +488,7 @@
         <v>Passing Scenarios</v>
       </c>
       <c r="B9">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -584,7 +584,7 @@
         <v>Match Arena &amp; Rounds Module</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -815,7 +815,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -963,9 +963,54 @@
         <v>2026-10-14</v>
       </c>
     </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>ARENA-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Match Arena &amp; Rounds</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Match Arena - Round Configuration, Live Scoring &amp; Team Registration</v>
+      </c>
+      <c r="D4" t="str">
+        <v>ARENA-03: Match Module Redesign - Horizontal capsules, relevance grouping, and interactive Championship Tree View</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Executes ARENA-03: Match Module Redesign - Horizontal capsules, relevance grouping, and interactive Championship Tree View. Grouped verification includes: Navigate to /matches and verify redesigned Matches page header and controls, Verify match capsules render in matches-grid or empty state handles cleanly, Toggle Group by Tournament view, Switch to Championship Tree View and verify interactive bracket tree, Switch back to Capsule Feed view.</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G4" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to /matches and verify redesigned Matches page header and controls
+2. Verify match capsules render in matches-grid or empty state handles cleanly
+3. Toggle Group by Tournament view
+4. Switch to Championship Tree View and verify interactive bracket tree
+5. Switch back to Capsule Feed view</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Successfully completes execution: Switch back to Capsule Feed view without errors.</v>
+      </c>
+      <c r="J4" t="str">
+        <v>apps/tt-client/tests/matches/match-arena.spec.ts</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="M4" t="str">
+        <v>2026-10-14</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1227,10 +1272,10 @@
         <v>Automated &amp; Passing</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-14</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-14</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -1271,10 +1316,10 @@
         <v>Automated &amp; Passing</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-14</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-14</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -1315,10 +1360,10 @@
         <v>Automated &amp; Passing</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-14</v>
       </c>
       <c r="M4" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-14</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -1360,10 +1405,10 @@
         <v>Automated &amp; Passing</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-14</v>
       </c>
       <c r="M5" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-14</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -1405,10 +1450,10 @@
         <v>Automated &amp; Passing</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-14</v>
       </c>
       <c r="M6" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-14</v>
       </c>
     </row>
   </sheetData>
@@ -2349,7 +2394,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -3541,19 +3586,19 @@
     </row>
     <row r="28" xml:space="preserve">
       <c r="A28" t="str">
-        <v>TT-001</v>
+        <v>ARENA-003</v>
       </c>
       <c r="B28" t="str">
-        <v>Table Tennis Matches</v>
+        <v>Match Arena &amp; Rounds</v>
       </c>
       <c r="C28" t="str">
-        <v>Table Tennis Matches &amp; Bracket Progression</v>
+        <v>Match Arena - Round Configuration, Live Scoring &amp; Team Registration</v>
       </c>
       <c r="D28" t="str">
-        <v>TT-01: Table Tennis Singles - 4 players bracket generation, set scores entry, winner advance to final, and champion crown</v>
+        <v>ARENA-03: Match Module Redesign - Horizontal capsules, relevance grouping, and interactive Championship Tree View</v>
       </c>
       <c r="E28" t="str">
-        <v>Executes TT-01: Table Tennis Singles - 4 players bracket generation, set scores entry, winner advance to final, and champion crown. Grouped verification includes: Create Table Tennis Singles tournament, Open tournament details and inspect overview, Seed 4 realistic players and verify automatic Round 1 bracket generation, Verify Round 1 matches render with two semifinal match pairings, Record scores for Semifinal Match 1 (11 - 7) and advance winner, Record scores for Semifinal Match 2 (8 - 11) and advance winner to Grand Final, Verify Grand Final match generated and record championship score (11 - 9), Verify Champion Victory Banner and final winner name.</v>
+        <v>Executes ARENA-03: Match Module Redesign - Horizontal capsules, relevance grouping, and interactive Championship Tree View. Grouped verification includes: Navigate to /matches and verify redesigned Matches page header and controls, Verify match capsules render in matches-grid or empty state handles cleanly, Toggle Group by Tournament view, Switch to Championship Tree View and verify interactive bracket tree, Switch back to Capsule Feed view.</v>
       </c>
       <c r="F28" t="str">
         <v>Functional E2E</v>
@@ -3562,6 +3607,51 @@
         <v>P1 (High)</v>
       </c>
       <c r="H28" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to /matches and verify redesigned Matches page header and controls
+2. Verify match capsules render in matches-grid or empty state handles cleanly
+3. Toggle Group by Tournament view
+4. Switch to Championship Tree View and verify interactive bracket tree
+5. Switch back to Capsule Feed view</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Successfully completes execution: Switch back to Capsule Feed view without errors.</v>
+      </c>
+      <c r="J28" t="str">
+        <v>apps/tt-client/tests/matches/match-arena.spec.ts</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L28" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="M28" t="str">
+        <v>2026-10-14</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>TT-001</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Table Tennis Matches</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Table Tennis Matches &amp; Bracket Progression</v>
+      </c>
+      <c r="D29" t="str">
+        <v>TT-01: Table Tennis Singles - 4 players bracket generation, set scores entry, winner advance to final, and champion crown</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Executes TT-01: Table Tennis Singles - 4 players bracket generation, set scores entry, winner advance to final, and champion crown. Grouped verification includes: Create Table Tennis Singles tournament, Open tournament details and inspect overview, Seed 4 realistic players and verify automatic Round 1 bracket generation, Verify Round 1 matches render with two semifinal match pairings, Record scores for Semifinal Match 1 (11 - 7) and advance winner, Record scores for Semifinal Match 2 (8 - 11) and advance winner to Grand Final, Verify Grand Final match generated and record championship score (11 - 9), Verify Champion Victory Banner and final winner name.</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Functional E2E</v>
+      </c>
+      <c r="G29" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H29" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create Table Tennis Singles tournament
 2. Open tournament details and inspect overview
 3. Seed 4 realistic players and verify automatic Round 1 bracket generation
@@ -3571,311 +3661,311 @@
 7. Verify Grand Final match generated and record championship score (11 - 9)
 8. Verify Champion Victory Banner and final winner name</v>
       </c>
-      <c r="I28" t="str">
+      <c r="I29" t="str">
         <v>Successfully completes execution: Verify Champion Victory Banner and final winner name without errors.</v>
       </c>
-      <c r="J28" t="str">
+      <c r="J29" t="str">
         <v>apps/tt-client/tests/matches/table-tennis.spec.ts</v>
       </c>
-      <c r="K28" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L28" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M28" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="29" xml:space="preserve">
-      <c r="A29" t="str">
+      <c r="K29" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L29" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M29" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
         <v>TT-002</v>
       </c>
-      <c r="B29" t="str">
+      <c r="B30" t="str">
         <v>Table Tennis Matches</v>
       </c>
-      <c r="C29" t="str">
+      <c r="C30" t="str">
         <v>Table Tennis Matches &amp; Bracket Progression</v>
       </c>
-      <c r="D29" t="str">
+      <c r="D30" t="str">
         <v>TT-02: Table Tennis Doubles - Team registration of 2-player pairs, Wave 1 draw, and set progression</v>
       </c>
-      <c r="E29" t="str">
+      <c r="E30" t="str">
         <v>Executes TT-02: Table Tennis Doubles - Team registration of 2-player pairs, Wave 1 draw, and set progression. Grouped verification includes: Create Table Tennis Doubles tournament (Team mode with team size 2), Open doubles tournament and seed 2-player pairs, Verify Wave 1 team matches rendered and record pair score.</v>
       </c>
-      <c r="F29" t="str">
+      <c r="F30" t="str">
         <v>Functional E2E</v>
       </c>
-      <c r="G29" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H29" t="str" xml:space="preserve">
+      <c r="G30" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H30" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create Table Tennis Doubles tournament (Team mode with team size 2)
 2. Open doubles tournament and seed 2-player pairs
 3. Verify Wave 1 team matches rendered and record pair score</v>
       </c>
-      <c r="I29" t="str">
+      <c r="I30" t="str">
         <v>Successfully completes execution: Verify Wave 1 team matches rendered and record pair score without errors.</v>
       </c>
-      <c r="J29" t="str">
+      <c r="J30" t="str">
         <v>apps/tt-client/tests/matches/table-tennis.spec.ts</v>
       </c>
-      <c r="K29" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L29" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M29" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="30" xml:space="preserve">
-      <c r="A30" t="str">
+      <c r="K30" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L30" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M30" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
         <v>SPRT-001</v>
       </c>
-      <c r="B30" t="str">
+      <c r="B31" t="str">
         <v>Multi-Sport Tournaments</v>
       </c>
-      <c r="C30" t="str">
+      <c r="C31" t="str">
         <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
       </c>
-      <c r="D30" t="str">
+      <c r="D31" t="str">
         <v>SPRT-01: Multi-Sport Form Adapters - sport presets auto-populate format, team limits, and rules</v>
       </c>
-      <c r="E30" t="str">
+      <c r="E31" t="str">
         <v>Executes SPRT-01: Multi-Sport Form Adapters - sport presets auto-populate format, team limits, and rules. Grouped verification includes: Navigate to Create Tournament page, Verify default Table Tennis preset configuration, Select Cricket sport card and verify adaptive fields for team competition, Select Chess sport card and verify scoring format is GAME_POINTS, Test quick rule template chip appending and live preview tab.</v>
       </c>
-      <c r="F30" t="str">
+      <c r="F31" t="str">
         <v>Functional E2E</v>
       </c>
-      <c r="G30" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H30" t="str" xml:space="preserve">
+      <c r="G31" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H31" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to Create Tournament page
 2. Verify default Table Tennis preset configuration
 3. Select Cricket sport card and verify adaptive fields for team competition
 4. Select Chess sport card and verify scoring format is GAME_POINTS
 5. Test quick rule template chip appending and live preview tab</v>
       </c>
-      <c r="I30" t="str">
+      <c r="I31" t="str">
         <v>Successfully completes execution: Test quick rule template chip appending and live preview tab without errors.</v>
       </c>
-      <c r="J30" t="str">
+      <c r="J31" t="str">
         <v>apps/tt-client/tests/multi-sport.spec.ts</v>
       </c>
-      <c r="K30" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L30" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M30" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="31" xml:space="preserve">
-      <c r="A31" t="str">
+      <c r="K31" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L31" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="M31" t="str">
+        <v>2026-10-14</v>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
         <v>SPRT-002</v>
       </c>
-      <c r="B31" t="str">
+      <c r="B32" t="str">
         <v>Multi-Sport Tournaments</v>
       </c>
-      <c r="C31" t="str">
+      <c r="C32" t="str">
         <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
       </c>
-      <c r="D31" t="str">
+      <c r="D32" t="str">
         <v>SPRT-02: Duplicate Registration Guard - prevents re-registration and displays Already Registered badge</v>
       </c>
-      <c r="E31" t="str">
+      <c r="E32" t="str">
         <v>Executes SPRT-02: Duplicate Registration Guard - prevents re-registration and displays Already Registered badge. Grouped verification includes: Create an individual tournament, Open tournament and register current user, Verify Hero now shows Already Registered badge and register button is removed, Verify user is listed in Participants tab.</v>
       </c>
-      <c r="F31" t="str">
+      <c r="F32" t="str">
         <v>UI / Functional</v>
       </c>
-      <c r="G31" t="str">
+      <c r="G32" t="str">
         <v>P0 (Critical)</v>
       </c>
-      <c r="H31" t="str" xml:space="preserve">
+      <c r="H32" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create an individual tournament
 2. Open tournament and register current user
 3. Verify Hero now shows Already Registered badge and register button is removed
 4. Verify user is listed in Participants tab</v>
       </c>
-      <c r="I31" t="str">
+      <c r="I32" t="str">
         <v>Successfully completes execution: Verify user is listed in Participants tab without errors.</v>
       </c>
-      <c r="J31" t="str">
+      <c r="J32" t="str">
         <v>apps/tt-client/tests/multi-sport.spec.ts</v>
       </c>
-      <c r="K31" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L31" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M31" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="32" xml:space="preserve">
-      <c r="A32" t="str">
+      <c r="K32" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L32" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="M32" t="str">
+        <v>2026-10-14</v>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
         <v>SPRT-003</v>
       </c>
-      <c r="B32" t="str">
+      <c r="B33" t="str">
         <v>Multi-Sport Tournaments</v>
       </c>
-      <c r="C32" t="str">
+      <c r="C33" t="str">
         <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
       </c>
-      <c r="D32" t="str">
+      <c r="D33" t="str">
         <v>SPRT-03: Team Sports Registration - team modal, min team size enforcement, and unique player assignment</v>
       </c>
-      <c r="E32" t="str">
+      <c r="E33" t="str">
         <v>Executes SPRT-03: Team Sports Registration - team modal, min team size enforcement, and unique player assignment. Grouped verification includes: Create a team Cricket tournament with minTeamSize = 2, Open Cricket tournament details and click Register Team, Verify Register Team Modal opens and enforces minimum team size, Add additional member and successfully submit team.</v>
       </c>
-      <c r="F32" t="str">
+      <c r="F33" t="str">
         <v>Functional E2E</v>
       </c>
-      <c r="G32" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H32" t="str" xml:space="preserve">
+      <c r="G33" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H33" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create a team Cricket tournament with minTeamSize = 2
 2. Open Cricket tournament details and click Register Team
 3. Verify Register Team Modal opens and enforces minimum team size
 4. Add additional member and successfully submit team</v>
       </c>
-      <c r="I32" t="str">
+      <c r="I33" t="str">
         <v>Successfully completes execution: Add additional member and successfully submit team without errors.</v>
       </c>
-      <c r="J32" t="str">
+      <c r="J33" t="str">
         <v>apps/tt-client/tests/multi-sport.spec.ts</v>
       </c>
-      <c r="K32" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L32" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M32" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="33" xml:space="preserve">
-      <c r="A33" t="str">
+      <c r="K33" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L33" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="M33" t="str">
+        <v>2026-10-14</v>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
         <v>SPRT-004</v>
       </c>
-      <c r="B33" t="str">
+      <c r="B34" t="str">
         <v>Multi-Sport Tournaments</v>
       </c>
-      <c r="C33" t="str">
+      <c r="C34" t="str">
         <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
       </c>
-      <c r="D33" t="str">
+      <c r="D34" t="str">
         <v>SPRT-04: Wave-by-Wave Progression &amp; Sport Scoring - registration lock, wave draws, sport-specific score entry, and finals crowning</v>
       </c>
-      <c r="E33" t="str">
+      <c r="E34" t="str">
         <v>Executes SPRT-04: Wave-by-Wave Progression &amp; Sport Scoring - registration lock, wave draws, sport-specific score entry, and finals crowning. Grouped verification includes: Create tournament and navigate to matches tab, Verify registration window status is initially open, Seed 4 dummy players to populate participants, Verify matches tab renders bracket round 1 with sport-specific scoring modal triggers, Complete remaining matches and verify Grand Final champion banner.</v>
       </c>
-      <c r="F33" t="str">
+      <c r="F34" t="str">
         <v>Functional E2E</v>
       </c>
-      <c r="G33" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H33" t="str" xml:space="preserve">
+      <c r="G34" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H34" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create tournament and navigate to matches tab
 2. Verify registration window status is initially open
 3. Seed 4 dummy players to populate participants
 4. Verify matches tab renders bracket round 1 with sport-specific scoring modal triggers
 5. Complete remaining matches and verify Grand Final champion banner</v>
       </c>
-      <c r="I33" t="str">
+      <c r="I34" t="str">
         <v>Successfully completes execution: Complete remaining matches and verify Grand Final champion banner without errors.</v>
       </c>
-      <c r="J33" t="str">
+      <c r="J34" t="str">
         <v>apps/tt-client/tests/multi-sport.spec.ts</v>
       </c>
-      <c r="K33" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L33" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M33" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="34" xml:space="preserve">
-      <c r="A34" t="str">
+      <c r="K34" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L34" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="M34" t="str">
+        <v>2026-10-14</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
         <v>SPRT-005</v>
       </c>
-      <c r="B34" t="str">
+      <c r="B35" t="str">
         <v>Multi-Sport Tournaments</v>
       </c>
-      <c r="C34" t="str">
+      <c r="C35" t="str">
         <v>Multi-Sport Tournaments, Team Registration &amp; Wave Fixtures</v>
       </c>
-      <c r="D34" t="str">
+      <c r="D35" t="str">
         <v>SPRT-06: Dual Division (Singles &amp; Doubles) - creates parent Championship with sub-tournaments, division switcher, and dual winners</v>
       </c>
-      <c r="E34" t="str">
+      <c r="E35" t="str">
         <v>Executes SPRT-06: Dual Division (Singles &amp; Doubles) - creates parent Championship with sub-tournaments, division switcher, and dual winners. Grouped verification includes: Navigate to Create Tournament page, Select Table Tennis and choose Dual Division mode, Verify unified parent tournament card displays Dual Division badge on Tournaments list, Open Championship details and verify Division Switcher tabs exist, Switch between Singles and Doubles divisions and verify separate sub-tournaments and rosters.</v>
       </c>
-      <c r="F34" t="str">
+      <c r="F35" t="str">
         <v>Functional E2E</v>
       </c>
-      <c r="G34" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H34" t="str" xml:space="preserve">
+      <c r="G35" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H35" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to Create Tournament page
 2. Select Table Tennis and choose Dual Division mode
 3. Verify unified parent tournament card displays Dual Division badge on Tournaments list
 4. Open Championship details and verify Division Switcher tabs exist
 5. Switch between Singles and Doubles divisions and verify separate sub-tournaments and rosters</v>
       </c>
-      <c r="I34" t="str">
+      <c r="I35" t="str">
         <v>Successfully completes execution: Switch between Singles and Doubles divisions and verify separate sub-tournaments and rosters without errors.</v>
       </c>
-      <c r="J34" t="str">
+      <c r="J35" t="str">
         <v>apps/tt-client/tests/multi-sport.spec.ts</v>
       </c>
-      <c r="K34" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L34" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M34" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="35" xml:space="preserve">
-      <c r="A35" t="str">
+      <c r="K35" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L35" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="M35" t="str">
+        <v>2026-10-14</v>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
         <v>NOTIF-001</v>
       </c>
-      <c r="B35" t="str">
+      <c r="B36" t="str">
         <v>Notification Center</v>
       </c>
-      <c r="C35" t="str">
+      <c r="C36" t="str">
         <v>Notification Center &amp; Sports Alerts System</v>
       </c>
-      <c r="D35" t="str">
+      <c r="D36" t="str">
         <v>NOTIF-01: Notification Dropdown &amp; Filtering - Unread badge, dropdown toggle, and category tabs</v>
       </c>
-      <c r="E35" t="str">
+      <c r="E36" t="str">
         <v>Executes NOTIF-01: Notification Dropdown &amp; Filtering - Unread badge, dropdown toggle, and category tabs. Grouped verification includes: Open landing page and inspect notification bell button, Click notification bell to open interactive dropdown, Verify initial dummy sports notifications rendered, Filter by Matches category and verify count, Filter by Tournaments category, Switch back to All filter tab.</v>
       </c>
-      <c r="F35" t="str">
+      <c r="F36" t="str">
         <v>State Transition</v>
       </c>
-      <c r="G35" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H35" t="str" xml:space="preserve">
+      <c r="G36" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H36" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Open landing page and inspect notification bell button
 2. Click notification bell to open interactive dropdown
 3. Verify initial dummy sports notifications rendered
@@ -3883,640 +3973,640 @@
 5. Filter by Tournaments category
 6. Switch back to All filter tab</v>
       </c>
-      <c r="I35" t="str">
+      <c r="I36" t="str">
         <v>Successfully completes execution: Switch back to All filter tab without errors.</v>
       </c>
-      <c r="J35" t="str">
+      <c r="J36" t="str">
         <v>apps/tt-client/tests/notifications.spec.ts</v>
       </c>
-      <c r="K35" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L35" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M35" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="36" xml:space="preserve">
-      <c r="A36" t="str">
+      <c r="K36" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L36" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M36" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
         <v>NOTIF-002</v>
       </c>
-      <c r="B36" t="str">
+      <c r="B37" t="str">
         <v>Notification Center</v>
       </c>
-      <c r="C36" t="str">
+      <c r="C37" t="str">
         <v>Notification Center &amp; Sports Alerts System</v>
       </c>
-      <c r="D36" t="str">
+      <c r="D37" t="str">
         <v>NOTIF-02: Notification Actions - Mark all as read and clear notifications</v>
       </c>
-      <c r="E36" t="str">
+      <c r="E37" t="str">
         <v>Executes NOTIF-02: Notification Actions - Mark all as read and clear notifications. Grouped verification includes: Open notification center dropdown, Click Mark all as read and verify unread badge dismissed, Click Clear all notifications and verify empty state rendered, Close notifications dropdown via close button.</v>
       </c>
-      <c r="F36" t="str">
+      <c r="F37" t="str">
         <v>Functional E2E</v>
       </c>
-      <c r="G36" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H36" t="str" xml:space="preserve">
+      <c r="G37" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H37" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Open notification center dropdown
 2. Click Mark all as read and verify unread badge dismissed
 3. Click Clear all notifications and verify empty state rendered
 4. Close notifications dropdown via close button</v>
       </c>
-      <c r="I36" t="str">
+      <c r="I37" t="str">
         <v>Successfully completes execution: Close notifications dropdown via close button without errors.</v>
       </c>
-      <c r="J36" t="str">
+      <c r="J37" t="str">
         <v>apps/tt-client/tests/notifications.spec.ts</v>
       </c>
-      <c r="K36" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L36" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M36" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="37" xml:space="preserve">
-      <c r="A37" t="str">
+      <c r="K37" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L37" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M37" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
         <v>SRV-001</v>
       </c>
-      <c r="B37" t="str">
+      <c r="B38" t="str">
         <v>Server Health &amp; Downtime</v>
       </c>
-      <c r="C37" t="str">
+      <c r="C38" t="str">
         <v>Server Health &amp; Downtime Error Handling</v>
       </c>
-      <c r="D37" t="str">
+      <c r="D38" t="str">
         <v>SRV-01: Server is down Banner - Displays user-friendly error when API gateway is unreachable</v>
       </c>
-      <c r="E37" t="str">
+      <c r="E38" t="str">
         <v>Executes SRV-01: Server is down Banner - Displays user-friendly error when API gateway is unreachable. Grouped verification includes: Navigate to landing page and observe network failure handling, Verify user-friendly Server is down banner is displayed, Verify Sidebar reflects Server Offline status, Verify Retry Connection action button exists on banner.</v>
       </c>
-      <c r="F37" t="str">
+      <c r="F38" t="str">
         <v>UI / Functional</v>
       </c>
-      <c r="G37" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H37" t="str" xml:space="preserve">
+      <c r="G38" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H38" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to landing page and observe network failure handling
 2. Verify user-friendly Server is down banner is displayed
 3. Verify Sidebar reflects Server Offline status
 4. Verify Retry Connection action button exists on banner</v>
       </c>
-      <c r="I37" t="str">
+      <c r="I38" t="str">
         <v>Successfully completes execution: Verify Retry Connection action button exists on banner without errors.</v>
       </c>
-      <c r="J37" t="str">
+      <c r="J38" t="str">
         <v>apps/tt-client/tests/server-health.spec.ts</v>
       </c>
-      <c r="K37" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L37" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M37" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="38" xml:space="preserve">
-      <c r="A38" t="str">
+      <c r="K38" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L38" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M38" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
         <v>SRV-002</v>
       </c>
-      <c r="B38" t="str">
+      <c r="B39" t="str">
         <v>Server Health &amp; Downtime</v>
       </c>
-      <c r="C38" t="str">
+      <c r="C39" t="str">
         <v>Server Health &amp; Downtime Error Handling</v>
       </c>
-      <c r="D38" t="str">
+      <c r="D39" t="str">
         <v>SRV-02: Server Downtime Recovery &amp; Dismissal - Dismissing banner and retry workflow</v>
       </c>
-      <c r="E38" t="str">
+      <c r="E39" t="str">
         <v>Executes SRV-02: Server Downtime Recovery &amp; Dismissal - Dismissing banner and retry workflow. Grouped verification includes: Navigate to application and trigger server down banner, Dismiss banner via close button and verify it hides.</v>
       </c>
-      <c r="F38" t="str">
+      <c r="F39" t="str">
         <v>Functional E2E</v>
       </c>
-      <c r="G38" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H38" t="str" xml:space="preserve">
+      <c r="G39" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H39" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to application and trigger server down banner
 2. Dismiss banner via close button and verify it hides</v>
       </c>
-      <c r="I38" t="str">
+      <c r="I39" t="str">
         <v>Successfully completes execution: Dismiss banner via close button and verify it hides without errors.</v>
       </c>
-      <c r="J38" t="str">
+      <c r="J39" t="str">
         <v>apps/tt-client/tests/server-health.spec.ts</v>
       </c>
-      <c r="K38" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L38" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M38" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39" t="str">
+      <c r="K39" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L39" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M39" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
         <v>TRN-001</v>
       </c>
-      <c r="B39" t="str">
+      <c r="B40" t="str">
         <v>Tournament Management</v>
       </c>
-      <c r="C39" t="str">
+      <c r="C40" t="str">
         <v>Tournament Management CRUD &amp; Validation Operations</v>
       </c>
-      <c r="D39" t="str">
+      <c r="D40" t="str">
         <v>CREATE: should create a new tournament successfully with valid data and show in directory</v>
       </c>
-      <c r="E39" t="str">
+      <c r="E40" t="str">
         <v>Executes CREATE: should create a new tournament successfully with valid data and show in directory. Grouped verification includes: Navigate to tournaments list, Open tournament creation form, Fill and submit tournament form with valid payload, Verify redirection back to tournaments directory, Search for created tournament and verify presence in grid.</v>
       </c>
-      <c r="F39" t="str">
+      <c r="F40" t="str">
         <v>CRUD - Create (Positive)</v>
       </c>
-      <c r="G39" t="str">
+      <c r="G40" t="str">
         <v>P0 (Critical)</v>
       </c>
-      <c r="H39" t="str" xml:space="preserve">
+      <c r="H40" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to tournaments list
 2. Open tournament creation form
 3. Fill and submit tournament form with valid payload
 4. Verify redirection back to tournaments directory
 5. Search for created tournament and verify presence in grid</v>
       </c>
-      <c r="I39" t="str">
+      <c r="I40" t="str">
         <v>Successfully completes execution: Search for created tournament and verify presence in grid without errors.</v>
       </c>
-      <c r="J39" t="str">
+      <c r="J40" t="str">
         <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
       </c>
-      <c r="K39" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L39" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M39" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="40" xml:space="preserve">
-      <c r="A40" t="str">
+      <c r="K40" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L40" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M40" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
         <v>TRN-002</v>
       </c>
-      <c r="B40" t="str">
+      <c r="B41" t="str">
         <v>Tournament Management</v>
       </c>
-      <c r="C40" t="str">
+      <c r="C41" t="str">
         <v>Tournament Management CRUD &amp; Validation Operations</v>
       </c>
-      <c r="D40" t="str">
+      <c r="D41" t="str">
         <v>VALIDATION: should enforce client-side date &amp; length constraints on tournament creation</v>
       </c>
-      <c r="E40" t="str">
+      <c r="E41" t="str">
         <v>Executes VALIDATION: should enforce client-side date &amp; length constraints on tournament creation. Grouped verification includes: Navigate to tournament creation page, Verify title minimum length constraint (&lt; 3 characters), Verify chronological date constraint (start date after registration deadline).</v>
       </c>
-      <c r="F40" t="str">
+      <c r="F41" t="str">
         <v>Validation (Negative)</v>
       </c>
-      <c r="G40" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H40" t="str" xml:space="preserve">
+      <c r="G41" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H41" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to tournament creation page
 2. Verify title minimum length constraint (&lt; 3 characters)
 3. Verify chronological date constraint (start date after registration deadline)</v>
       </c>
-      <c r="I40" t="str">
+      <c r="I41" t="str">
         <v>Successfully completes execution: Verify chronological date constraint (start date after registration deadline) without errors.</v>
       </c>
-      <c r="J40" t="str">
+      <c r="J41" t="str">
         <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
       </c>
-      <c r="K40" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L40" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M40" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="41" xml:space="preserve">
-      <c r="A41" t="str">
+      <c r="K41" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L41" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M41" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
         <v>TRN-003</v>
       </c>
-      <c r="B41" t="str">
+      <c r="B42" t="str">
         <v>Tournament Management</v>
       </c>
-      <c r="C41" t="str">
+      <c r="C42" t="str">
         <v>Tournament Management CRUD &amp; Validation Operations</v>
       </c>
-      <c r="D41" t="str">
+      <c r="D42" t="str">
         <v>READ: should navigate to tournament details and inspect overview, participants, and tabs</v>
       </c>
-      <c r="E41" t="str">
+      <c r="E42" t="str">
         <v>Executes READ: should navigate to tournament details and inspect overview, participants, and tabs. Grouped verification includes: Create tournament prerequisite, Search and navigate to tournament details page, Switch between tabs and verify content containers.</v>
       </c>
-      <c r="F41" t="str">
+      <c r="F42" t="str">
         <v>CRUD - Read (Positive)</v>
       </c>
-      <c r="G41" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H41" t="str" xml:space="preserve">
+      <c r="G42" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H42" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create tournament prerequisite
 2. Search and navigate to tournament details page
 3. Switch between tabs and verify content containers</v>
       </c>
-      <c r="I41" t="str">
+      <c r="I42" t="str">
         <v>Successfully completes execution: Switch between tabs and verify content containers without errors.</v>
       </c>
-      <c r="J41" t="str">
+      <c r="J42" t="str">
         <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
       </c>
-      <c r="K41" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L41" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M41" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="42" xml:space="preserve">
-      <c r="A42" t="str">
+      <c r="K42" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L42" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M42" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
         <v>TRN-004</v>
       </c>
-      <c r="B42" t="str">
+      <c r="B43" t="str">
         <v>Tournament Management</v>
       </c>
-      <c r="C42" t="str">
+      <c r="C43" t="str">
         <v>Tournament Management CRUD &amp; Validation Operations</v>
       </c>
-      <c r="D42" t="str">
+      <c r="D43" t="str">
         <v>UPDATE: should edit tournament details from settings tab and verify updates in real-time</v>
       </c>
-      <c r="E42" t="str">
+      <c r="E43" t="str">
         <v>Executes UPDATE: should edit tournament details from settings tab and verify updates in real-time. Grouped verification includes: Create tournament prerequisite, Navigate to tournament details page, Update tournament settings with new fields, Verify success alert and updated hero title in real-time.</v>
       </c>
-      <c r="F42" t="str">
+      <c r="F43" t="str">
         <v>CRUD - Update (Positive)</v>
       </c>
-      <c r="G42" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H42" t="str" xml:space="preserve">
+      <c r="G43" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H43" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create tournament prerequisite
 2. Navigate to tournament details page
 3. Update tournament settings with new fields
 4. Verify success alert and updated hero title in real-time</v>
       </c>
-      <c r="I42" t="str">
+      <c r="I43" t="str">
         <v>Successfully completes execution: Verify success alert and updated hero title in real-time without errors.</v>
       </c>
-      <c r="J42" t="str">
+      <c r="J43" t="str">
         <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
       </c>
-      <c r="K42" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L42" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M42" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="43" xml:space="preserve">
-      <c r="A43" t="str">
+      <c r="K43" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L43" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M43" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
         <v>TRN-005</v>
       </c>
-      <c r="B43" t="str">
+      <c r="B44" t="str">
         <v>Tournament Management</v>
       </c>
-      <c r="C43" t="str">
+      <c r="C44" t="str">
         <v>Tournament Management CRUD &amp; Validation Operations</v>
       </c>
-      <c r="D43" t="str">
+      <c r="D44" t="str">
         <v>STATUS &amp; REGISTRATION: should change operational status and allow player registration</v>
       </c>
-      <c r="E43" t="str">
+      <c r="E44" t="str">
         <v>Executes STATUS &amp; REGISTRATION: should change operational status and allow player registration. Grouped verification includes: Create tournament prerequisite, Navigate to tournament details page, Change status to ACTIVE via Settings tab, Register current authenticated user for tournament, Verify participant count incremented.</v>
       </c>
-      <c r="F43" t="str">
+      <c r="F44" t="str">
         <v>State Transition</v>
       </c>
-      <c r="G43" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H43" t="str" xml:space="preserve">
+      <c r="G44" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H44" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create tournament prerequisite
 2. Navigate to tournament details page
 3. Change status to ACTIVE via Settings tab
 4. Register current authenticated user for tournament
 5. Verify participant count incremented</v>
       </c>
-      <c r="I43" t="str">
+      <c r="I44" t="str">
         <v>Successfully completes execution: Verify participant count incremented without errors.</v>
       </c>
-      <c r="J43" t="str">
+      <c r="J44" t="str">
         <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
       </c>
-      <c r="K43" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L43" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M43" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="44" xml:space="preserve">
-      <c r="A44" t="str">
+      <c r="K44" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L44" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M44" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
         <v>TRN-006</v>
       </c>
-      <c r="B44" t="str">
+      <c r="B45" t="str">
         <v>Tournament Management</v>
       </c>
-      <c r="C44" t="str">
+      <c r="C45" t="str">
         <v>Tournament Management CRUD &amp; Validation Operations</v>
       </c>
-      <c r="D44" t="str">
+      <c r="D45" t="str">
         <v>DELETE: should soft-delete tournament and verify removal from directory</v>
       </c>
-      <c r="E44" t="str">
+      <c r="E45" t="str">
         <v>Executes DELETE: should soft-delete tournament and verify removal from directory. Grouped verification includes: Create tournament prerequisite, Navigate to tournament details page, Accept confirmation dialog and delete tournament from hero, Verify redirection and tournament removed from directory.</v>
       </c>
-      <c r="F44" t="str">
+      <c r="F45" t="str">
         <v>CRUD - Delete</v>
       </c>
-      <c r="G44" t="str">
+      <c r="G45" t="str">
         <v>P0 (Critical)</v>
       </c>
-      <c r="H44" t="str" xml:space="preserve">
+      <c r="H45" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create tournament prerequisite
 2. Navigate to tournament details page
 3. Accept confirmation dialog and delete tournament from hero
 4. Verify redirection and tournament removed from directory</v>
       </c>
-      <c r="I44" t="str">
+      <c r="I45" t="str">
         <v>Successfully completes execution: Verify redirection and tournament removed from directory without errors.</v>
       </c>
-      <c r="J44" t="str">
+      <c r="J45" t="str">
         <v>apps/tt-client/tests/tournament-crud.spec.ts</v>
       </c>
-      <c r="K44" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L44" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M44" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="45" xml:space="preserve">
-      <c r="A45" t="str">
+      <c r="K45" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L45" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M45" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
         <v>USER-001</v>
       </c>
-      <c r="B45" t="str">
+      <c r="B46" t="str">
         <v>Member Management</v>
       </c>
-      <c r="C45" t="str">
+      <c r="C46" t="str">
         <v>User &amp; Member Management CRUD Operations</v>
       </c>
-      <c r="D45" t="str">
+      <c r="D46" t="str">
         <v>CREATE: should create a new user/member successfully and display in directory</v>
       </c>
-      <c r="E45" t="str">
+      <c r="E46" t="str">
         <v>Executes CREATE: should create a new user/member successfully and display in directory. Grouped verification includes: Navigate to member management directory, Open user creation form, Fill and submit user creation form with DataFactory payload, Verify redirection back to member directory, Search for the newly created user and verify presence in table.</v>
       </c>
-      <c r="F45" t="str">
+      <c r="F46" t="str">
         <v>CRUD - Create (Positive)</v>
       </c>
-      <c r="G45" t="str">
+      <c r="G46" t="str">
         <v>P0 (Critical)</v>
       </c>
-      <c r="H45" t="str" xml:space="preserve">
+      <c r="H46" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to member management directory
 2. Open user creation form
 3. Fill and submit user creation form with DataFactory payload
 4. Verify redirection back to member directory
 5. Search for the newly created user and verify presence in table</v>
       </c>
-      <c r="I45" t="str">
+      <c r="I46" t="str">
         <v>Successfully completes execution: Search for the newly created user and verify presence in table without errors.</v>
       </c>
-      <c r="J45" t="str">
+      <c r="J46" t="str">
         <v>apps/tt-client/tests/user-crud.spec.ts</v>
       </c>
-      <c r="K45" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L45" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M45" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="46" xml:space="preserve">
-      <c r="A46" t="str">
+      <c r="K46" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L46" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M46" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
         <v>USER-002</v>
       </c>
-      <c r="B46" t="str">
+      <c r="B47" t="str">
         <v>Member Management</v>
       </c>
-      <c r="C46" t="str">
+      <c r="C47" t="str">
         <v>User &amp; Member Management CRUD Operations</v>
       </c>
-      <c r="D46" t="str">
+      <c r="D47" t="str">
         <v>READ: should navigate to user profile and view complete details</v>
       </c>
-      <c r="E46" t="str">
+      <c r="E47" t="str">
         <v>Executes READ: should navigate to user profile and view complete details. Grouped verification includes: Create user for profile inspection, Filter/search to locate the created user, Click user name link to navigate to details page, Verify member details page renders with matching identity.</v>
       </c>
-      <c r="F46" t="str">
+      <c r="F47" t="str">
         <v>CRUD - Read (Positive)</v>
       </c>
-      <c r="G46" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H46" t="str" xml:space="preserve">
+      <c r="G47" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H47" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create user for profile inspection
 2. Filter/search to locate the created user
 3. Click user name link to navigate to details page
 4. Verify member details page renders with matching identity</v>
       </c>
-      <c r="I46" t="str">
+      <c r="I47" t="str">
         <v>Successfully completes execution: Verify member details page renders with matching identity without errors.</v>
       </c>
-      <c r="J46" t="str">
+      <c r="J47" t="str">
         <v>apps/tt-client/tests/user-crud.spec.ts</v>
       </c>
-      <c r="K46" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L46" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M46" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="47" xml:space="preserve">
-      <c r="A47" t="str">
+      <c r="K47" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L47" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M47" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
         <v>USER-003</v>
       </c>
-      <c r="B47" t="str">
+      <c r="B48" t="str">
         <v>Member Management</v>
       </c>
-      <c r="C47" t="str">
+      <c r="C48" t="str">
         <v>User &amp; Member Management CRUD Operations</v>
       </c>
-      <c r="D47" t="str">
+      <c r="D48" t="str">
         <v>UPDATE: should update user details (name, role, status) and verify changes</v>
       </c>
-      <c r="E47" t="str">
+      <c r="E48" t="str">
         <v>Executes UPDATE: should update user details (name, role, status) and verify changes. Grouped verification includes: Create target user for updating, Locate user and open edit page via action dropdown, Apply updates to user details, Verify redirection to profile and updated details.</v>
       </c>
-      <c r="F47" t="str">
+      <c r="F48" t="str">
         <v>CRUD - Update (Positive)</v>
       </c>
-      <c r="G47" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H47" t="str" xml:space="preserve">
+      <c r="G48" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H48" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create target user for updating
 2. Locate user and open edit page via action dropdown
 3. Apply updates to user details
 4. Verify redirection to profile and updated details</v>
       </c>
-      <c r="I47" t="str">
+      <c r="I48" t="str">
         <v>Successfully completes execution: Verify redirection to profile and updated details without errors.</v>
       </c>
-      <c r="J47" t="str">
+      <c r="J48" t="str">
         <v>apps/tt-client/tests/user-crud.spec.ts</v>
       </c>
-      <c r="K47" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L47" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M47" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="48" xml:space="preserve">
-      <c r="A48" t="str">
+      <c r="K48" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L48" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M48" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str">
         <v>USER-004</v>
       </c>
-      <c r="B48" t="str">
+      <c r="B49" t="str">
         <v>Member Management</v>
       </c>
-      <c r="C48" t="str">
+      <c r="C49" t="str">
         <v>User &amp; Member Management CRUD Operations</v>
       </c>
-      <c r="D48" t="str">
+      <c r="D49" t="str">
         <v>STATUS TOGGLE: should toggle user account status between active and inactive</v>
       </c>
-      <c r="E48" t="str">
+      <c r="E49" t="str">
         <v>Executes STATUS TOGGLE: should toggle user account status between active and inactive. Grouped verification includes: Create user for status toggling, Search for the member in directory, Open dropdown menu and toggle account status, Verify status badge updates to Inactive.</v>
       </c>
-      <c r="F48" t="str">
+      <c r="F49" t="str">
         <v>State Transition</v>
       </c>
-      <c r="G48" t="str">
-        <v>P1 (High)</v>
-      </c>
-      <c r="H48" t="str" xml:space="preserve">
+      <c r="G49" t="str">
+        <v>P1 (High)</v>
+      </c>
+      <c r="H49" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create user for status toggling
 2. Search for the member in directory
 3. Open dropdown menu and toggle account status
 4. Verify status badge updates to Inactive</v>
       </c>
-      <c r="I48" t="str">
+      <c r="I49" t="str">
         <v>Successfully completes execution: Verify status badge updates to Inactive without errors.</v>
       </c>
-      <c r="J48" t="str">
+      <c r="J49" t="str">
         <v>apps/tt-client/tests/user-crud.spec.ts</v>
       </c>
-      <c r="K48" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L48" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M48" t="str">
-        <v>2026-10-13</v>
-      </c>
-    </row>
-    <row r="49" xml:space="preserve">
-      <c r="A49" t="str">
+      <c r="K49" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L49" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M49" t="str">
+        <v>2026-10-13</v>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
         <v>USER-005</v>
       </c>
-      <c r="B49" t="str">
+      <c r="B50" t="str">
         <v>Member Management</v>
       </c>
-      <c r="C49" t="str">
+      <c r="C50" t="str">
         <v>User &amp; Member Management CRUD Operations</v>
       </c>
-      <c r="D49" t="str">
+      <c r="D50" t="str">
         <v>DELETE: should soft-delete user and verify removal from directory</v>
       </c>
-      <c r="E49" t="str">
+      <c r="E50" t="str">
         <v>Executes DELETE: should soft-delete user and verify removal from directory. Grouped verification includes: Create user to delete, Search and locate member in directory, Navigate to details page and trigger deletion with confirmation dialog, Verify redirected to /members and user is no longer listed.</v>
       </c>
-      <c r="F49" t="str">
+      <c r="F50" t="str">
         <v>CRUD - Delete</v>
       </c>
-      <c r="G49" t="str">
+      <c r="G50" t="str">
         <v>P0 (Critical)</v>
       </c>
-      <c r="H49" t="str" xml:space="preserve">
+      <c r="H50" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Create user to delete
 2. Search and locate member in directory
 3. Navigate to details page and trigger deletion with confirmation dialog
 4. Verify redirected to /members and user is no longer listed</v>
       </c>
-      <c r="I49" t="str">
+      <c r="I50" t="str">
         <v>Successfully completes execution: Verify redirected to /members and user is no longer listed without errors.</v>
       </c>
-      <c r="J49" t="str">
+      <c r="J50" t="str">
         <v>apps/tt-client/tests/user-crud.spec.ts</v>
       </c>
-      <c r="K49" t="str">
-        <v>Automated &amp; Passing</v>
-      </c>
-      <c r="L49" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="M49" t="str">
+      <c r="K50" t="str">
+        <v>Automated &amp; Passing</v>
+      </c>
+      <c r="L50" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="M50" t="str">
         <v>2026-10-13</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M50"/>
   </ignoredErrors>
 </worksheet>
 </file>
